--- a/data/2026-2027/Présences.xlsx
+++ b/data/2026-2027/Présences.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F4CF047-2849-E540-A556-9C8C96AE5106}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33202625-8DDA-CE43-AF76-2A082F6760E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{2EF0EE96-8EE0-C649-8161-B8679CB6F342}"/>
   </bookViews>
@@ -146,13 +146,13 @@
     <t>Ismail Mediouna</t>
   </si>
   <si>
-    <t xml:space="preserve">Fares </t>
-  </si>
-  <si>
     <t>Donald Onana</t>
   </si>
   <si>
     <t>Brady</t>
+  </si>
+  <si>
+    <t>Fares Farhi</t>
   </si>
 </sst>
 </file>
@@ -209,75 +209,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1616,7 +1548,7 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B24" s="3">
         <f t="shared" si="9"/>
@@ -1660,7 +1592,7 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B25" s="3">
         <f t="shared" si="9"/>
@@ -1748,7 +1680,7 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B27" s="3">
         <f t="shared" ref="B27:B29" si="11">COUNTA(K27:VR27)</f>

--- a/data/2026-2027/Présences.xlsx
+++ b/data/2026-2027/Présences.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33202625-8DDA-CE43-AF76-2A082F6760E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A22BD3A-6335-D44D-AB8A-3A1EA6961315}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{2EF0EE96-8EE0-C649-8161-B8679CB6F342}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="38">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -134,9 +134,6 @@
     <t>Sandro Marcon</t>
   </si>
   <si>
-    <t xml:space="preserve">Bradley </t>
-  </si>
-  <si>
     <t>Pharell Cafara</t>
   </si>
   <si>
@@ -149,10 +146,10 @@
     <t>Donald Onana</t>
   </si>
   <si>
-    <t>Brady</t>
-  </si>
-  <si>
     <t>Fares Farhi</t>
+  </si>
+  <si>
+    <t>Brady Gouandjia</t>
   </si>
 </sst>
 </file>
@@ -539,13 +536,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0866E353-69CC-CA42-AE0E-F860DC308060}">
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" ht="51" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -579,14 +576,20 @@
       <c r="K1" s="4">
         <v>46216</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L1" s="4">
+        <v>46217</v>
+      </c>
+      <c r="M1" s="4">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="3">
         <f>COUNTA(K2:VR2)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C2" s="3">
         <f>COUNTIF(K2:VR2,"P")</f>
@@ -614,7 +617,7 @@
       </c>
       <c r="I2" s="3">
         <f>COUNTIF(K2:VW2,"RH")</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J2" s="3">
         <f>COUNTIF(K2:VW2,"S")</f>
@@ -623,18 +626,24 @@
       <c r="K2" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="3">
         <f t="shared" ref="B3:B21" si="2">COUNTA(K3:VR3)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C3" s="3">
         <f t="shared" ref="C3:C21" si="3">COUNTIF(K3:VR3,"P")</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D3" s="5">
         <f t="shared" ref="D3:D26" si="4">COUNTIF(K3:VR3,"REP")</f>
@@ -667,18 +676,24 @@
       <c r="K3" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>24</v>
       </c>
       <c r="B4" s="3">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C4" s="3">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D4" s="5">
         <f t="shared" si="4"/>
@@ -711,18 +726,24 @@
       <c r="K4" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="3">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C5" s="3">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D5" s="5">
         <f t="shared" si="4"/>
@@ -755,18 +776,24 @@
       <c r="K5" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>25</v>
       </c>
       <c r="B6" s="3">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C6" s="3">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D6" s="5">
         <f t="shared" si="4"/>
@@ -799,18 +826,24 @@
       <c r="K6" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>26</v>
       </c>
       <c r="B7" s="3">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C7" s="3">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D7" s="5">
         <f t="shared" si="4"/>
@@ -843,18 +876,24 @@
       <c r="K7" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>27</v>
       </c>
       <c r="B8" s="3">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C8" s="3">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D8" s="5">
         <f t="shared" si="4"/>
@@ -887,18 +926,24 @@
       <c r="K8" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="3">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C9" s="3">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D9" s="5">
         <f t="shared" si="4"/>
@@ -931,18 +976,24 @@
       <c r="K9" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>28</v>
       </c>
       <c r="B10" s="3">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C10" s="3">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D10" s="5">
         <f t="shared" si="4"/>
@@ -975,18 +1026,24 @@
       <c r="K10" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="3">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C11" s="3">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D11" s="5">
         <f t="shared" si="4"/>
@@ -1019,18 +1076,24 @@
       <c r="K11" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>13</v>
       </c>
       <c r="B12" s="3">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C12" s="3">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D12" s="5">
         <f t="shared" si="4"/>
@@ -1063,18 +1126,24 @@
       <c r="K12" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>23</v>
       </c>
       <c r="B13" s="3">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C13" s="3">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D13" s="5">
         <f t="shared" si="4"/>
@@ -1107,18 +1176,24 @@
       <c r="K13" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>14</v>
       </c>
       <c r="B14" s="3">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C14" s="3">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D14" s="5">
         <f t="shared" si="4"/>
@@ -1151,18 +1226,24 @@
       <c r="K14" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>29</v>
       </c>
       <c r="B15" s="3">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C15" s="3">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D15" s="5">
         <f t="shared" si="4"/>
@@ -1195,18 +1276,24 @@
       <c r="K15" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>30</v>
       </c>
       <c r="B16" s="3">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C16" s="3">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D16" s="5">
         <f t="shared" si="4"/>
@@ -1239,18 +1326,24 @@
       <c r="K16" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>31</v>
       </c>
       <c r="B17" s="3">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C17" s="3">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D17" s="5">
         <f t="shared" si="4"/>
@@ -1283,18 +1376,24 @@
       <c r="K17" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L17" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>21</v>
       </c>
       <c r="B18" s="3">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" s="3">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D18" s="5">
         <f t="shared" si="4"/>
@@ -1327,18 +1426,24 @@
       <c r="K18" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L18" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>16</v>
       </c>
       <c r="B19" s="3">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C19" s="3">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D19" s="5">
         <f t="shared" si="4"/>
@@ -1371,18 +1476,24 @@
       <c r="K19" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B20" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C20" s="3">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D20" s="5">
         <f t="shared" si="4"/>
@@ -1412,19 +1523,27 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="K20" s="3"/>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K20" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B21" s="3">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C21" s="3">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D21" s="5">
         <f t="shared" si="4"/>
@@ -1457,18 +1576,24 @@
       <c r="K21" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B22" s="3">
         <f t="shared" ref="B22:B26" si="9">COUNTA(K22:VR22)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C22" s="3">
         <f t="shared" ref="C22:C26" si="10">COUNTIF(K22:VR22,"P")</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D22" s="5">
         <f t="shared" si="4"/>
@@ -1501,18 +1626,24 @@
       <c r="K22" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B23" s="3">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C23" s="3">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D23" s="5">
         <f t="shared" si="4"/>
@@ -1545,18 +1676,24 @@
       <c r="K23" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L23" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B24" s="3">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C24" s="3">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D24" s="5">
         <f t="shared" si="4"/>
@@ -1589,14 +1726,20 @@
       <c r="K24" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B25" s="3">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C25" s="3">
         <f t="shared" si="10"/>
@@ -1608,7 +1751,7 @@
       </c>
       <c r="E25" s="3">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F25" s="3">
         <f t="shared" si="1"/>
@@ -1633,18 +1776,24 @@
       <c r="K25" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="M25" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>15</v>
       </c>
       <c r="B26" s="3">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C26" s="3">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D26" s="5">
         <f t="shared" si="4"/>
@@ -1677,18 +1826,21 @@
       <c r="K26" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>37</v>
-      </c>
+      <c r="L26" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B27" s="3">
         <f t="shared" ref="B27:B29" si="11">COUNTA(K27:VR27)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C27" s="3">
         <f t="shared" ref="C27:C29" si="12">COUNTIF(K27:VR27,"P")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27" s="5">
         <f t="shared" ref="D27:D29" si="13">COUNTIF(K27:VR27,"REP")</f>
@@ -1718,11 +1870,11 @@
         <f t="shared" ref="J27:J29" si="19">COUNTIF(K27:VW27,"S")</f>
         <v>0</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K27" s="3"/>
+      <c r="L27" s="3"/>
+      <c r="M27" s="3"/>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B28" s="3">
         <f t="shared" si="11"/>
         <v>0</v>
@@ -1760,7 +1912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B29" s="3">
         <f t="shared" si="11"/>
         <v>0</v>
@@ -1798,7 +1950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B30" s="3">
         <f t="shared" ref="B30" si="20">COUNTA(K30:VR30)</f>
         <v>0</v>
@@ -1836,7 +1988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B31" s="3">
         <f t="shared" ref="B31" si="29">COUNTA(K31:VR31)</f>
         <v>0</v>
@@ -1874,7 +2026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B32" s="3">
         <f t="shared" ref="B32" si="38">COUNTA(K32:VR32)</f>
         <v>0</v>

--- a/data/2026-2027/Présences.xlsx
+++ b/data/2026-2027/Présences.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A22BD3A-6335-D44D-AB8A-3A1EA6961315}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28A1F302-50AD-A446-A37E-D1D33D541AC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{2EF0EE96-8EE0-C649-8161-B8679CB6F342}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="40">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -150,6 +150,12 @@
   </si>
   <si>
     <t>Brady Gouandjia</t>
+  </si>
+  <si>
+    <t>Romain Antunes</t>
+  </si>
+  <si>
+    <t>Kamal Bafounta</t>
   </si>
 </sst>
 </file>
@@ -536,13 +542,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0866E353-69CC-CA42-AE0E-F860DC308060}">
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:N32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -582,14 +588,17 @@
       <c r="M1" s="4">
         <v>46218</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N1" s="4">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="3">
         <f>COUNTA(K2:VR2)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" s="3">
         <f>COUNTIF(K2:VR2,"P")</f>
@@ -617,7 +626,7 @@
       </c>
       <c r="I2" s="3">
         <f>COUNTIF(K2:VW2,"RH")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J2" s="3">
         <f>COUNTIF(K2:VW2,"S")</f>
@@ -632,18 +641,21 @@
       <c r="M2" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N2" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="3">
         <f t="shared" ref="B3:B21" si="2">COUNTA(K3:VR3)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3" s="3">
         <f t="shared" ref="C3:C21" si="3">COUNTIF(K3:VR3,"P")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" s="5">
         <f t="shared" ref="D3:D26" si="4">COUNTIF(K3:VR3,"REP")</f>
@@ -682,18 +694,21 @@
       <c r="M3" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N3" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>24</v>
       </c>
       <c r="B4" s="3">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" s="3">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" s="5">
         <f t="shared" si="4"/>
@@ -732,18 +747,21 @@
       <c r="M4" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N4" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="3">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" s="3">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5" s="5">
         <f t="shared" si="4"/>
@@ -782,18 +800,21 @@
       <c r="M5" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N5" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>25</v>
       </c>
       <c r="B6" s="3">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6" s="3">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6" s="5">
         <f t="shared" si="4"/>
@@ -832,18 +853,21 @@
       <c r="M6" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N6" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>26</v>
       </c>
       <c r="B7" s="3">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C7" s="3">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D7" s="5">
         <f t="shared" si="4"/>
@@ -882,18 +906,21 @@
       <c r="M7" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N7" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>27</v>
       </c>
       <c r="B8" s="3">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C8" s="3">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D8" s="5">
         <f t="shared" si="4"/>
@@ -932,18 +959,21 @@
       <c r="M8" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N8" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="3">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" s="3">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D9" s="5">
         <f t="shared" si="4"/>
@@ -982,18 +1012,21 @@
       <c r="M9" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>28</v>
       </c>
       <c r="B10" s="3">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" s="3">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" s="5">
         <f t="shared" si="4"/>
@@ -1032,18 +1065,21 @@
       <c r="M10" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="3">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" s="3">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D11" s="5">
         <f t="shared" si="4"/>
@@ -1082,18 +1118,21 @@
       <c r="M11" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>13</v>
       </c>
       <c r="B12" s="3">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C12" s="3">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D12" s="5">
         <f t="shared" si="4"/>
@@ -1132,18 +1171,21 @@
       <c r="M12" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>23</v>
       </c>
       <c r="B13" s="3">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C13" s="3">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D13" s="5">
         <f t="shared" si="4"/>
@@ -1182,18 +1224,21 @@
       <c r="M13" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>14</v>
       </c>
       <c r="B14" s="3">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C14" s="3">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D14" s="5">
         <f t="shared" si="4"/>
@@ -1232,18 +1277,21 @@
       <c r="M14" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N14" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>29</v>
       </c>
       <c r="B15" s="3">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" s="3">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D15" s="5">
         <f t="shared" si="4"/>
@@ -1282,18 +1330,21 @@
       <c r="M15" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N15" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>30</v>
       </c>
       <c r="B16" s="3">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" s="3">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D16" s="5">
         <f t="shared" si="4"/>
@@ -1332,18 +1383,21 @@
       <c r="M16" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>31</v>
       </c>
       <c r="B17" s="3">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C17" s="3">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D17" s="5">
         <f t="shared" si="4"/>
@@ -1382,18 +1436,21 @@
       <c r="M17" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N17" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>21</v>
       </c>
       <c r="B18" s="3">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C18" s="3">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D18" s="5">
         <f t="shared" si="4"/>
@@ -1432,18 +1489,21 @@
       <c r="M18" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N18" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>16</v>
       </c>
       <c r="B19" s="3">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C19" s="3">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D19" s="5">
         <f t="shared" si="4"/>
@@ -1482,18 +1542,21 @@
       <c r="M19" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>37</v>
       </c>
       <c r="B20" s="3">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C20" s="3">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D20" s="5">
         <f t="shared" si="4"/>
@@ -1532,18 +1595,21 @@
       <c r="M20" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N20" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>32</v>
       </c>
       <c r="B21" s="3">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C21" s="3">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D21" s="5">
         <f t="shared" si="4"/>
@@ -1582,18 +1648,21 @@
       <c r="M21" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N21" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>33</v>
       </c>
       <c r="B22" s="3">
         <f t="shared" ref="B22:B26" si="9">COUNTA(K22:VR22)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C22" s="3">
         <f t="shared" ref="C22:C26" si="10">COUNTIF(K22:VR22,"P")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D22" s="5">
         <f t="shared" si="4"/>
@@ -1632,18 +1701,21 @@
       <c r="M22" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>34</v>
       </c>
       <c r="B23" s="3">
         <f t="shared" si="9"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C23" s="3">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D23" s="5">
         <f t="shared" si="4"/>
@@ -1682,18 +1754,21 @@
       <c r="M23" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N23" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>36</v>
       </c>
       <c r="B24" s="3">
         <f t="shared" si="9"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C24" s="3">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D24" s="5">
         <f t="shared" si="4"/>
@@ -1732,14 +1807,17 @@
       <c r="M24" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N24" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>35</v>
       </c>
       <c r="B25" s="3">
         <f t="shared" si="9"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C25" s="3">
         <f t="shared" si="10"/>
@@ -1751,7 +1829,7 @@
       </c>
       <c r="E25" s="3">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F25" s="3">
         <f t="shared" si="1"/>
@@ -1782,18 +1860,21 @@
       <c r="M25" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>15</v>
       </c>
       <c r="B26" s="3">
         <f t="shared" si="9"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C26" s="3">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D26" s="5">
         <f t="shared" si="4"/>
@@ -1832,15 +1913,21 @@
       <c r="M26" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N26" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>38</v>
+      </c>
       <c r="B27" s="3">
         <f t="shared" ref="B27:B29" si="11">COUNTA(K27:VR27)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C27" s="3">
         <f t="shared" ref="C27:C29" si="12">COUNTIF(K27:VR27,"P")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D27" s="5">
         <f t="shared" ref="D27:D29" si="13">COUNTIF(K27:VR27,"REP")</f>
@@ -1873,8 +1960,14 @@
       <c r="K27" s="3"/>
       <c r="L27" s="3"/>
       <c r="M27" s="3"/>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N27" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>39</v>
+      </c>
       <c r="B28" s="3">
         <f t="shared" si="11"/>
         <v>0</v>
@@ -1912,7 +2005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B29" s="3">
         <f t="shared" si="11"/>
         <v>0</v>
@@ -1950,7 +2043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B30" s="3">
         <f t="shared" ref="B30" si="20">COUNTA(K30:VR30)</f>
         <v>0</v>
@@ -1988,7 +2081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B31" s="3">
         <f t="shared" ref="B31" si="29">COUNTA(K31:VR31)</f>
         <v>0</v>
@@ -2026,7 +2119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B32" s="3">
         <f t="shared" ref="B32" si="38">COUNTA(K32:VR32)</f>
         <v>0</v>

--- a/data/2026-2027/Présences.xlsx
+++ b/data/2026-2027/Présences.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28A1F302-50AD-A446-A37E-D1D33D541AC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC99F1F6-6862-2944-A990-C184EDD38F9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{2EF0EE96-8EE0-C649-8161-B8679CB6F342}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="40">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -542,13 +542,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0866E353-69CC-CA42-AE0E-F860DC308060}">
-  <dimension ref="A1:N32"/>
+  <dimension ref="A1:O32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" ht="51" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -591,14 +591,17 @@
       <c r="N1" s="4">
         <v>46219</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O1" s="4">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="3">
         <f>COUNTA(K2:VR2)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" s="3">
         <f>COUNTIF(K2:VR2,"P")</f>
@@ -626,7 +629,7 @@
       </c>
       <c r="I2" s="3">
         <f>COUNTIF(K2:VW2,"RH")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J2" s="3">
         <f>COUNTIF(K2:VW2,"S")</f>
@@ -644,18 +647,21 @@
       <c r="N2" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O2" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="3">
         <f t="shared" ref="B3:B21" si="2">COUNTA(K3:VR3)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3" s="3">
         <f t="shared" ref="C3:C21" si="3">COUNTIF(K3:VR3,"P")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3" s="5">
         <f t="shared" ref="D3:D26" si="4">COUNTIF(K3:VR3,"REP")</f>
@@ -697,18 +703,21 @@
       <c r="N3" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O3" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>24</v>
       </c>
       <c r="B4" s="3">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4" s="3">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" s="5">
         <f t="shared" si="4"/>
@@ -750,18 +759,21 @@
       <c r="N4" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O4" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="3">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C5" s="3">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5" s="5">
         <f t="shared" si="4"/>
@@ -803,18 +815,21 @@
       <c r="N5" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O5" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>25</v>
       </c>
       <c r="B6" s="3">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6" s="3">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" s="5">
         <f t="shared" si="4"/>
@@ -856,18 +871,21 @@
       <c r="N6" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O6" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>26</v>
       </c>
       <c r="B7" s="3">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C7" s="3">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D7" s="5">
         <f t="shared" si="4"/>
@@ -909,18 +927,21 @@
       <c r="N7" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O7" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>27</v>
       </c>
       <c r="B8" s="3">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C8" s="3">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D8" s="5">
         <f t="shared" si="4"/>
@@ -962,18 +983,21 @@
       <c r="N8" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="3">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C9" s="3">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D9" s="5">
         <f t="shared" si="4"/>
@@ -1015,18 +1039,21 @@
       <c r="N9" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>28</v>
       </c>
       <c r="B10" s="3">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C10" s="3">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D10" s="5">
         <f t="shared" si="4"/>
@@ -1068,18 +1095,21 @@
       <c r="N10" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="3">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C11" s="3">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D11" s="5">
         <f t="shared" si="4"/>
@@ -1121,18 +1151,21 @@
       <c r="N11" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>13</v>
       </c>
       <c r="B12" s="3">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" s="3">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D12" s="5">
         <f t="shared" si="4"/>
@@ -1174,18 +1207,21 @@
       <c r="N12" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>23</v>
       </c>
       <c r="B13" s="3">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C13" s="3">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D13" s="5">
         <f t="shared" si="4"/>
@@ -1227,18 +1263,21 @@
       <c r="N13" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>14</v>
       </c>
       <c r="B14" s="3">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C14" s="3">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D14" s="5">
         <f t="shared" si="4"/>
@@ -1280,18 +1319,21 @@
       <c r="N14" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>29</v>
       </c>
       <c r="B15" s="3">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C15" s="3">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D15" s="5">
         <f t="shared" si="4"/>
@@ -1333,18 +1375,21 @@
       <c r="N15" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>30</v>
       </c>
       <c r="B16" s="3">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C16" s="3">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D16" s="5">
         <f t="shared" si="4"/>
@@ -1386,18 +1431,21 @@
       <c r="N16" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>31</v>
       </c>
       <c r="B17" s="3">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C17" s="3">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D17" s="5">
         <f t="shared" si="4"/>
@@ -1439,18 +1487,21 @@
       <c r="N17" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O17" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>21</v>
       </c>
       <c r="B18" s="3">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C18" s="3">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D18" s="5">
         <f t="shared" si="4"/>
@@ -1492,18 +1543,21 @@
       <c r="N18" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O18" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>16</v>
       </c>
       <c r="B19" s="3">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C19" s="3">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D19" s="5">
         <f t="shared" si="4"/>
@@ -1545,18 +1599,21 @@
       <c r="N19" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>37</v>
       </c>
       <c r="B20" s="3">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C20" s="3">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D20" s="5">
         <f t="shared" si="4"/>
@@ -1598,18 +1655,21 @@
       <c r="N20" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O20" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>32</v>
       </c>
       <c r="B21" s="3">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C21" s="3">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D21" s="5">
         <f t="shared" si="4"/>
@@ -1651,18 +1711,21 @@
       <c r="N21" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>33</v>
       </c>
       <c r="B22" s="3">
         <f t="shared" ref="B22:B26" si="9">COUNTA(K22:VR22)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C22" s="3">
         <f t="shared" ref="C22:C26" si="10">COUNTIF(K22:VR22,"P")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D22" s="5">
         <f t="shared" si="4"/>
@@ -1704,18 +1767,21 @@
       <c r="N22" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>34</v>
       </c>
       <c r="B23" s="3">
         <f t="shared" si="9"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C23" s="3">
         <f t="shared" si="10"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D23" s="5">
         <f t="shared" si="4"/>
@@ -1757,14 +1823,17 @@
       <c r="N23" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O23" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>36</v>
       </c>
       <c r="B24" s="3">
         <f t="shared" si="9"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C24" s="3">
         <f t="shared" si="10"/>
@@ -1792,7 +1861,7 @@
       </c>
       <c r="I24" s="3">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" s="3">
         <f t="shared" si="8"/>
@@ -1808,20 +1877,23 @@
         <v>7</v>
       </c>
       <c r="N24" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>35</v>
       </c>
       <c r="B25" s="3">
         <f t="shared" si="9"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C25" s="3">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D25" s="5">
         <f t="shared" si="4"/>
@@ -1829,7 +1901,7 @@
       </c>
       <c r="E25" s="3">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F25" s="3">
         <f t="shared" si="1"/>
@@ -1858,23 +1930,26 @@
         <v>18</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="N25" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7</v>
+      </c>
+      <c r="O25" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>15</v>
       </c>
       <c r="B26" s="3">
         <f t="shared" si="9"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C26" s="3">
         <f t="shared" si="10"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D26" s="5">
         <f t="shared" si="4"/>
@@ -1916,18 +1991,21 @@
       <c r="N26" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O26" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>38</v>
       </c>
       <c r="B27" s="3">
         <f t="shared" ref="B27:B29" si="11">COUNTA(K27:VR27)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C27" s="3">
         <f t="shared" ref="C27:C29" si="12">COUNTIF(K27:VR27,"P")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D27" s="5">
         <f t="shared" ref="D27:D29" si="13">COUNTIF(K27:VR27,"REP")</f>
@@ -1963,18 +2041,21 @@
       <c r="N27" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O27" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>39</v>
       </c>
       <c r="B28" s="3">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C28" s="3">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D28" s="5">
         <f t="shared" si="13"/>
@@ -2004,8 +2085,11 @@
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B29" s="3">
         <f t="shared" si="11"/>
         <v>0</v>
@@ -2043,7 +2127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B30" s="3">
         <f t="shared" ref="B30" si="20">COUNTA(K30:VR30)</f>
         <v>0</v>
@@ -2081,7 +2165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B31" s="3">
         <f t="shared" ref="B31" si="29">COUNTA(K31:VR31)</f>
         <v>0</v>
@@ -2119,7 +2203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B32" s="3">
         <f t="shared" ref="B32" si="38">COUNTA(K32:VR32)</f>
         <v>0</v>

--- a/data/2026-2027/Présences.xlsx
+++ b/data/2026-2027/Présences.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC99F1F6-6862-2944-A990-C184EDD38F9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DFACC56-D522-9647-BD6C-98386E84D7DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{2EF0EE96-8EE0-C649-8161-B8679CB6F342}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="41">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -156,6 +156,9 @@
   </si>
   <si>
     <t>Kamal Bafounta</t>
+  </si>
+  <si>
+    <t>21/07/2026 (1)</t>
   </si>
 </sst>
 </file>
@@ -191,7 +194,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -207,6 +210,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -542,13 +548,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0866E353-69CC-CA42-AE0E-F860DC308060}">
-  <dimension ref="A1:O32"/>
+  <dimension ref="A1:Q32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17" ht="51" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -594,14 +600,20 @@
       <c r="O1" s="4">
         <v>46220</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P1" s="4">
+        <v>46223</v>
+      </c>
+      <c r="Q1" s="6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="3">
         <f>COUNTA(K2:VR2)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C2" s="3">
         <f>COUNTIF(K2:VR2,"P")</f>
@@ -629,7 +641,7 @@
       </c>
       <c r="I2" s="3">
         <f>COUNTIF(K2:VW2,"RH")</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J2" s="3">
         <f>COUNTIF(K2:VW2,"S")</f>
@@ -650,14 +662,20 @@
       <c r="O2" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="3">
         <f t="shared" ref="B3:B21" si="2">COUNTA(K3:VR3)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C3" s="3">
         <f t="shared" ref="C3:C21" si="3">COUNTIF(K3:VR3,"P")</f>
@@ -669,7 +687,7 @@
       </c>
       <c r="E3" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F3" s="3">
         <f t="shared" si="1"/>
@@ -706,18 +724,24 @@
       <c r="O3" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>24</v>
       </c>
       <c r="B4" s="3">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C4" s="3">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D4" s="5">
         <f t="shared" si="4"/>
@@ -762,18 +786,24 @@
       <c r="O4" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="3">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C5" s="3">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D5" s="5">
         <f t="shared" si="4"/>
@@ -818,18 +848,24 @@
       <c r="O5" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q5" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>25</v>
       </c>
       <c r="B6" s="3">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C6" s="3">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D6" s="5">
         <f t="shared" si="4"/>
@@ -874,18 +910,24 @@
       <c r="O6" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q6" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>26</v>
       </c>
       <c r="B7" s="3">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C7" s="3">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D7" s="5">
         <f t="shared" si="4"/>
@@ -930,18 +972,24 @@
       <c r="O7" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q7" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>27</v>
       </c>
       <c r="B8" s="3">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C8" s="3">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D8" s="5">
         <f t="shared" si="4"/>
@@ -986,18 +1034,24 @@
       <c r="O8" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="3">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C9" s="3">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D9" s="5">
         <f t="shared" si="4"/>
@@ -1042,18 +1096,24 @@
       <c r="O9" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>28</v>
       </c>
       <c r="B10" s="3">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C10" s="3">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D10" s="5">
         <f t="shared" si="4"/>
@@ -1098,18 +1158,24 @@
       <c r="O10" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="3">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C11" s="3">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D11" s="5">
         <f t="shared" si="4"/>
@@ -1154,18 +1220,24 @@
       <c r="O11" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q11" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>13</v>
       </c>
       <c r="B12" s="3">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C12" s="3">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D12" s="5">
         <f t="shared" si="4"/>
@@ -1210,18 +1282,24 @@
       <c r="O12" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>23</v>
       </c>
       <c r="B13" s="3">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C13" s="3">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D13" s="5">
         <f t="shared" si="4"/>
@@ -1266,18 +1344,24 @@
       <c r="O13" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q13" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>14</v>
       </c>
       <c r="B14" s="3">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C14" s="3">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D14" s="5">
         <f t="shared" si="4"/>
@@ -1322,18 +1406,24 @@
       <c r="O14" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>29</v>
       </c>
       <c r="B15" s="3">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C15" s="3">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D15" s="5">
         <f t="shared" si="4"/>
@@ -1378,18 +1468,24 @@
       <c r="O15" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>30</v>
       </c>
       <c r="B16" s="3">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C16" s="3">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D16" s="5">
         <f t="shared" si="4"/>
@@ -1434,18 +1530,24 @@
       <c r="O16" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q16" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>31</v>
       </c>
       <c r="B17" s="3">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C17" s="3">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D17" s="5">
         <f t="shared" si="4"/>
@@ -1490,18 +1592,24 @@
       <c r="O17" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>21</v>
       </c>
       <c r="B18" s="3">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C18" s="3">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D18" s="5">
         <f t="shared" si="4"/>
@@ -1546,18 +1654,24 @@
       <c r="O18" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>16</v>
       </c>
       <c r="B19" s="3">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C19" s="3">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D19" s="5">
         <f t="shared" si="4"/>
@@ -1602,18 +1716,24 @@
       <c r="O19" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q19" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>37</v>
       </c>
       <c r="B20" s="3">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C20" s="3">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D20" s="5">
         <f t="shared" si="4"/>
@@ -1658,18 +1778,24 @@
       <c r="O20" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>32</v>
       </c>
       <c r="B21" s="3">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C21" s="3">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D21" s="5">
         <f t="shared" si="4"/>
@@ -1714,18 +1840,24 @@
       <c r="O21" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>33</v>
       </c>
       <c r="B22" s="3">
         <f t="shared" ref="B22:B26" si="9">COUNTA(K22:VR22)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C22" s="3">
         <f t="shared" ref="C22:C26" si="10">COUNTIF(K22:VR22,"P")</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D22" s="5">
         <f t="shared" si="4"/>
@@ -1770,18 +1902,24 @@
       <c r="O22" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>34</v>
       </c>
       <c r="B23" s="3">
         <f t="shared" si="9"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C23" s="3">
         <f t="shared" si="10"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D23" s="5">
         <f t="shared" si="4"/>
@@ -1826,18 +1964,24 @@
       <c r="O23" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>36</v>
       </c>
       <c r="B24" s="3">
         <f t="shared" si="9"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C24" s="3">
         <f t="shared" si="10"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D24" s="5">
         <f t="shared" si="4"/>
@@ -1882,18 +2026,24 @@
       <c r="O24" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>35</v>
       </c>
       <c r="B25" s="3">
         <f t="shared" si="9"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C25" s="3">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D25" s="5">
         <f t="shared" si="4"/>
@@ -1938,18 +2088,24 @@
       <c r="O25" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q25" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>15</v>
       </c>
       <c r="B26" s="3">
         <f t="shared" si="9"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C26" s="3">
         <f t="shared" si="10"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D26" s="5">
         <f t="shared" si="4"/>
@@ -1994,18 +2150,24 @@
       <c r="O26" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>38</v>
       </c>
       <c r="B27" s="3">
         <f t="shared" ref="B27:B29" si="11">COUNTA(K27:VR27)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C27" s="3">
         <f t="shared" ref="C27:C29" si="12">COUNTIF(K27:VR27,"P")</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D27" s="5">
         <f t="shared" ref="D27:D29" si="13">COUNTIF(K27:VR27,"REP")</f>
@@ -2044,18 +2206,24 @@
       <c r="O27" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>39</v>
       </c>
       <c r="B28" s="3">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C28" s="3">
         <f t="shared" si="12"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D28" s="5">
         <f t="shared" si="13"/>
@@ -2088,8 +2256,14 @@
       <c r="O28" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q28" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B29" s="3">
         <f t="shared" si="11"/>
         <v>0</v>
@@ -2127,7 +2301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B30" s="3">
         <f t="shared" ref="B30" si="20">COUNTA(K30:VR30)</f>
         <v>0</v>
@@ -2165,7 +2339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B31" s="3">
         <f t="shared" ref="B31" si="29">COUNTA(K31:VR31)</f>
         <v>0</v>
@@ -2203,7 +2377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B32" s="3">
         <f t="shared" ref="B32" si="38">COUNTA(K32:VR32)</f>
         <v>0</v>

--- a/data/2026-2027/Présences.xlsx
+++ b/data/2026-2027/Présences.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DFACC56-D522-9647-BD6C-98386E84D7DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B2ED97B-CCE9-2640-A919-CB22CD289149}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{2EF0EE96-8EE0-C649-8161-B8679CB6F342}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="46">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -159,6 +159,21 @@
   </si>
   <si>
     <t>21/07/2026 (1)</t>
+  </si>
+  <si>
+    <t>21/07/2026 (2)</t>
+  </si>
+  <si>
+    <t>22/07/2026 (1)</t>
+  </si>
+  <si>
+    <t>22/07/2026 (2)</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>23/07/2026 (1)</t>
   </si>
 </sst>
 </file>
@@ -548,13 +563,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0866E353-69CC-CA42-AE0E-F860DC308060}">
-  <dimension ref="A1:Q32"/>
+  <dimension ref="A1:U32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" ht="51" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -606,14 +621,26 @@
       <c r="Q1" s="6" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R1" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="S1" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="T1" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="U1" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="3">
         <f>COUNTA(K2:VR2)</f>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C2" s="3">
         <f>COUNTIF(K2:VR2,"P")</f>
@@ -641,7 +668,7 @@
       </c>
       <c r="I2" s="3">
         <f>COUNTIF(K2:VW2,"RH")</f>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J2" s="3">
         <f>COUNTIF(K2:VW2,"S")</f>
@@ -668,14 +695,26 @@
       <c r="Q2" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U2" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="3">
         <f t="shared" ref="B3:B21" si="2">COUNTA(K3:VR3)</f>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C3" s="3">
         <f t="shared" ref="C3:C21" si="3">COUNTIF(K3:VR3,"P")</f>
@@ -687,7 +726,7 @@
       </c>
       <c r="E3" s="3">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F3" s="3">
         <f t="shared" si="1"/>
@@ -730,18 +769,30 @@
       <c r="Q3" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="S3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="T3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="U3" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>24</v>
       </c>
       <c r="B4" s="3">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C4" s="3">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D4" s="5">
         <f t="shared" si="4"/>
@@ -792,18 +843,30 @@
       <c r="Q4" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="S4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="T4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="U4" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="3">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C5" s="3">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D5" s="5">
         <f t="shared" si="4"/>
@@ -854,18 +917,30 @@
       <c r="Q5" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="S5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="T5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="U5" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>25</v>
       </c>
       <c r="B6" s="3">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C6" s="3">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D6" s="5">
         <f t="shared" si="4"/>
@@ -916,14 +991,26 @@
       <c r="Q6" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="S6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="T6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="U6" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>26</v>
       </c>
       <c r="B7" s="3">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C7" s="3">
         <f t="shared" si="3"/>
@@ -939,7 +1026,7 @@
       </c>
       <c r="F7" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G7" s="3">
         <f t="shared" si="5"/>
@@ -978,18 +1065,30 @@
       <c r="Q7" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="S7" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="T7" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="U7" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>27</v>
       </c>
       <c r="B8" s="3">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C8" s="3">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D8" s="5">
         <f t="shared" si="4"/>
@@ -1040,18 +1139,30 @@
       <c r="Q8" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="S8" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="T8" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="U8" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="3">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C9" s="3">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D9" s="5">
         <f t="shared" si="4"/>
@@ -1102,18 +1213,30 @@
       <c r="Q9" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="T9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="U9" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>28</v>
       </c>
       <c r="B10" s="3">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C10" s="3">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D10" s="5">
         <f t="shared" si="4"/>
@@ -1125,7 +1248,7 @@
       </c>
       <c r="F10" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G10" s="3">
         <f t="shared" si="5"/>
@@ -1164,18 +1287,30 @@
       <c r="Q10" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="T10" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="U10" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="3">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C11" s="3">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D11" s="5">
         <f t="shared" si="4"/>
@@ -1226,18 +1361,30 @@
       <c r="Q11" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="S11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="T11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="U11" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>13</v>
       </c>
       <c r="B12" s="3">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C12" s="3">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D12" s="5">
         <f t="shared" si="4"/>
@@ -1288,18 +1435,30 @@
       <c r="Q12" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="T12" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="U12" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>23</v>
       </c>
       <c r="B13" s="3">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C13" s="3">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D13" s="5">
         <f t="shared" si="4"/>
@@ -1350,18 +1509,30 @@
       <c r="Q13" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="S13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="T13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="U13" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>14</v>
       </c>
       <c r="B14" s="3">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C14" s="3">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D14" s="5">
         <f t="shared" si="4"/>
@@ -1412,18 +1583,30 @@
       <c r="Q14" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="U14" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>29</v>
       </c>
       <c r="B15" s="3">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C15" s="3">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D15" s="5">
         <f t="shared" si="4"/>
@@ -1474,18 +1657,30 @@
       <c r="Q15" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="S15" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="T15" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="U15" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>30</v>
       </c>
       <c r="B16" s="3">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C16" s="3">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D16" s="5">
         <f t="shared" si="4"/>
@@ -1536,18 +1731,30 @@
       <c r="Q16" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="S16" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="T16" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="U16" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>31</v>
       </c>
       <c r="B17" s="3">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C17" s="3">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D17" s="5">
         <f t="shared" si="4"/>
@@ -1598,18 +1805,30 @@
       <c r="Q17" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="T17" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="U17" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>21</v>
       </c>
       <c r="B18" s="3">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C18" s="3">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D18" s="5">
         <f t="shared" si="4"/>
@@ -1660,18 +1879,30 @@
       <c r="Q18" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="T18" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="U18" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>16</v>
       </c>
       <c r="B19" s="3">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C19" s="3">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D19" s="5">
         <f t="shared" si="4"/>
@@ -1722,18 +1953,30 @@
       <c r="Q19" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="S19" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="T19" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="U19" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>37</v>
       </c>
       <c r="B20" s="3">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C20" s="3">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D20" s="5">
         <f t="shared" si="4"/>
@@ -1784,18 +2027,30 @@
       <c r="Q20" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="T20" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="U20" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>32</v>
       </c>
       <c r="B21" s="3">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C21" s="3">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D21" s="5">
         <f t="shared" si="4"/>
@@ -1846,18 +2101,30 @@
       <c r="Q21" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="T21" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="U21" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>33</v>
       </c>
       <c r="B22" s="3">
         <f t="shared" ref="B22:B26" si="9">COUNTA(K22:VR22)</f>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C22" s="3">
         <f t="shared" ref="C22:C26" si="10">COUNTIF(K22:VR22,"P")</f>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D22" s="5">
         <f t="shared" si="4"/>
@@ -1908,18 +2175,30 @@
       <c r="Q22" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="T22" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="U22" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>34</v>
       </c>
       <c r="B23" s="3">
         <f t="shared" si="9"/>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C23" s="3">
         <f t="shared" si="10"/>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D23" s="5">
         <f t="shared" si="4"/>
@@ -1927,7 +2206,7 @@
       </c>
       <c r="E23" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" s="3">
         <f t="shared" si="1"/>
@@ -1970,18 +2249,30 @@
       <c r="Q23" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="S23" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="T23" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="U23" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>36</v>
       </c>
       <c r="B24" s="3">
         <f t="shared" si="9"/>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C24" s="3">
         <f t="shared" si="10"/>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D24" s="5">
         <f t="shared" si="4"/>
@@ -2032,18 +2323,30 @@
       <c r="Q24" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="T24" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="U24" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>35</v>
       </c>
       <c r="B25" s="3">
         <f t="shared" si="9"/>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C25" s="3">
         <f t="shared" si="10"/>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D25" s="5">
         <f t="shared" si="4"/>
@@ -2094,18 +2397,30 @@
       <c r="Q25" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="S25" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="T25" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="U25" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>15</v>
       </c>
       <c r="B26" s="3">
         <f t="shared" si="9"/>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C26" s="3">
         <f t="shared" si="10"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D26" s="5">
         <f t="shared" si="4"/>
@@ -2117,7 +2432,7 @@
       </c>
       <c r="F26" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G26" s="3">
         <f t="shared" si="5"/>
@@ -2156,18 +2471,30 @@
       <c r="Q26" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="S26" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="T26" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="U26" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>38</v>
       </c>
       <c r="B27" s="3">
         <f t="shared" ref="B27:B29" si="11">COUNTA(K27:VR27)</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C27" s="3">
         <f t="shared" ref="C27:C29" si="12">COUNTIF(K27:VR27,"P")</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D27" s="5">
         <f t="shared" ref="D27:D29" si="13">COUNTIF(K27:VR27,"REP")</f>
@@ -2212,18 +2539,30 @@
       <c r="Q27" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="S27" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="T27" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="U27" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>39</v>
       </c>
       <c r="B28" s="3">
         <f t="shared" si="11"/>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C28" s="3">
         <f t="shared" si="12"/>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D28" s="5">
         <f t="shared" si="13"/>
@@ -2262,8 +2601,20 @@
       <c r="Q28" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="S28" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="T28" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="U28" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B29" s="3">
         <f t="shared" si="11"/>
         <v>0</v>
@@ -2301,7 +2652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B30" s="3">
         <f t="shared" ref="B30" si="20">COUNTA(K30:VR30)</f>
         <v>0</v>
@@ -2339,7 +2690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B31" s="3">
         <f t="shared" ref="B31" si="29">COUNTA(K31:VR31)</f>
         <v>0</v>
@@ -2377,7 +2728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B32" s="3">
         <f t="shared" ref="B32" si="38">COUNTA(K32:VR32)</f>
         <v>0</v>

--- a/data/2026-2027/Présences.xlsx
+++ b/data/2026-2027/Présences.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B2ED97B-CCE9-2640-A919-CB22CD289149}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BD9386B-AA15-7241-9AE6-88E1410748FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{2EF0EE96-8EE0-C649-8161-B8679CB6F342}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="47">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -174,6 +174,9 @@
   </si>
   <si>
     <t>23/07/2026 (1)</t>
+  </si>
+  <si>
+    <t>23/07/2026 (2)</t>
   </si>
 </sst>
 </file>
@@ -563,13 +566,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0866E353-69CC-CA42-AE0E-F860DC308060}">
-  <dimension ref="A1:U32"/>
+  <dimension ref="A1:W32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:23" ht="51" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -633,14 +636,20 @@
       <c r="U1" s="6" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V1" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="W1" s="6">
+        <v>46227</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="3">
         <f>COUNTA(K2:VR2)</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C2" s="3">
         <f>COUNTIF(K2:VR2,"P")</f>
@@ -668,7 +677,7 @@
       </c>
       <c r="I2" s="3">
         <f>COUNTIF(K2:VW2,"RH")</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J2" s="3">
         <f>COUNTIF(K2:VW2,"S")</f>
@@ -707,14 +716,20 @@
       <c r="U2" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="W2" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="3">
         <f t="shared" ref="B3:B21" si="2">COUNTA(K3:VR3)</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C3" s="3">
         <f t="shared" ref="C3:C21" si="3">COUNTIF(K3:VR3,"P")</f>
@@ -726,7 +741,7 @@
       </c>
       <c r="E3" s="3">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F3" s="3">
         <f t="shared" si="1"/>
@@ -781,18 +796,24 @@
       <c r="U3" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W3" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>24</v>
       </c>
       <c r="B4" s="3">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C4" s="3">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D4" s="5">
         <f t="shared" si="4"/>
@@ -855,18 +876,24 @@
       <c r="U4" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="W4" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="3">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C5" s="3">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D5" s="5">
         <f t="shared" si="4"/>
@@ -929,18 +956,24 @@
       <c r="U5" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="W5" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>25</v>
       </c>
       <c r="B6" s="3">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C6" s="3">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D6" s="5">
         <f t="shared" si="4"/>
@@ -1003,14 +1036,20 @@
       <c r="U6" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="W6" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>26</v>
       </c>
       <c r="B7" s="3">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C7" s="3">
         <f t="shared" si="3"/>
@@ -1026,7 +1065,7 @@
       </c>
       <c r="F7" s="3">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G7" s="3">
         <f t="shared" si="5"/>
@@ -1077,18 +1116,24 @@
       <c r="U7" s="3" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V7" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="W7" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>27</v>
       </c>
       <c r="B8" s="3">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C8" s="3">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D8" s="5">
         <f t="shared" si="4"/>
@@ -1151,18 +1196,24 @@
       <c r="U8" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V8" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="W8" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="3">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C9" s="3">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D9" s="5">
         <f t="shared" si="4"/>
@@ -1174,7 +1225,7 @@
       </c>
       <c r="F9" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" s="3">
         <f t="shared" si="5"/>
@@ -1225,18 +1276,24 @@
       <c r="U9" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="W9" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>28</v>
       </c>
       <c r="B10" s="3">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C10" s="3">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D10" s="5">
         <f t="shared" si="4"/>
@@ -1299,18 +1356,24 @@
       <c r="U10" s="3" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="W10" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="3">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C11" s="3">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D11" s="5">
         <f t="shared" si="4"/>
@@ -1373,18 +1436,24 @@
       <c r="U11" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="W11" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>13</v>
       </c>
       <c r="B12" s="3">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C12" s="3">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D12" s="5">
         <f t="shared" si="4"/>
@@ -1447,18 +1516,24 @@
       <c r="U12" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="W12" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>23</v>
       </c>
       <c r="B13" s="3">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C13" s="3">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D13" s="5">
         <f t="shared" si="4"/>
@@ -1521,18 +1596,24 @@
       <c r="U13" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="W13" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>14</v>
       </c>
       <c r="B14" s="3">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C14" s="3">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D14" s="5">
         <f t="shared" si="4"/>
@@ -1595,18 +1676,24 @@
       <c r="U14" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="W14" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>29</v>
       </c>
       <c r="B15" s="3">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C15" s="3">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D15" s="5">
         <f t="shared" si="4"/>
@@ -1669,18 +1756,24 @@
       <c r="U15" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="W15" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>30</v>
       </c>
       <c r="B16" s="3">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C16" s="3">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D16" s="5">
         <f t="shared" si="4"/>
@@ -1743,18 +1836,24 @@
       <c r="U16" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="W16" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>31</v>
       </c>
       <c r="B17" s="3">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C17" s="3">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D17" s="5">
         <f t="shared" si="4"/>
@@ -1817,18 +1916,24 @@
       <c r="U17" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V17" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="W17" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>21</v>
       </c>
       <c r="B18" s="3">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C18" s="3">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D18" s="5">
         <f t="shared" si="4"/>
@@ -1891,18 +1996,24 @@
       <c r="U18" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V18" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="W18" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>16</v>
       </c>
       <c r="B19" s="3">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C19" s="3">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D19" s="5">
         <f t="shared" si="4"/>
@@ -1965,18 +2076,24 @@
       <c r="U19" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="W19" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>37</v>
       </c>
       <c r="B20" s="3">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C20" s="3">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D20" s="5">
         <f t="shared" si="4"/>
@@ -2039,18 +2156,24 @@
       <c r="U20" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="W20" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>32</v>
       </c>
       <c r="B21" s="3">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C21" s="3">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D21" s="5">
         <f t="shared" si="4"/>
@@ -2113,18 +2236,24 @@
       <c r="U21" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="W21" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>33</v>
       </c>
       <c r="B22" s="3">
         <f t="shared" ref="B22:B26" si="9">COUNTA(K22:VR22)</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C22" s="3">
         <f t="shared" ref="C22:C26" si="10">COUNTIF(K22:VR22,"P")</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D22" s="5">
         <f t="shared" si="4"/>
@@ -2187,18 +2316,24 @@
       <c r="U22" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="W22" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>34</v>
       </c>
       <c r="B23" s="3">
         <f t="shared" si="9"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C23" s="3">
         <f t="shared" si="10"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D23" s="5">
         <f t="shared" si="4"/>
@@ -2261,18 +2396,24 @@
       <c r="U23" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V23" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="W23" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>36</v>
       </c>
       <c r="B24" s="3">
         <f t="shared" si="9"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C24" s="3">
         <f t="shared" si="10"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D24" s="5">
         <f t="shared" si="4"/>
@@ -2335,18 +2476,24 @@
       <c r="U24" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="W24" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>35</v>
       </c>
       <c r="B25" s="3">
         <f t="shared" si="9"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C25" s="3">
         <f t="shared" si="10"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D25" s="5">
         <f t="shared" si="4"/>
@@ -2409,14 +2556,20 @@
       <c r="U25" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="W25" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>15</v>
       </c>
       <c r="B26" s="3">
         <f t="shared" si="9"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C26" s="3">
         <f t="shared" si="10"/>
@@ -2432,7 +2585,7 @@
       </c>
       <c r="F26" s="3">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G26" s="3">
         <f t="shared" si="5"/>
@@ -2483,18 +2636,24 @@
       <c r="U26" s="3" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V26" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="W26" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>38</v>
       </c>
       <c r="B27" s="3">
         <f t="shared" ref="B27:B29" si="11">COUNTA(K27:VR27)</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C27" s="3">
         <f t="shared" ref="C27:C29" si="12">COUNTIF(K27:VR27,"P")</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D27" s="5">
         <f t="shared" ref="D27:D29" si="13">COUNTIF(K27:VR27,"REP")</f>
@@ -2551,18 +2710,24 @@
       <c r="U27" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V27" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="W27" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>39</v>
       </c>
       <c r="B28" s="3">
         <f t="shared" si="11"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C28" s="3">
         <f t="shared" si="12"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D28" s="5">
         <f t="shared" si="13"/>
@@ -2613,8 +2778,14 @@
       <c r="U28" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="W28" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B29" s="3">
         <f t="shared" si="11"/>
         <v>0</v>
@@ -2652,7 +2823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B30" s="3">
         <f t="shared" ref="B30" si="20">COUNTA(K30:VR30)</f>
         <v>0</v>
@@ -2690,7 +2861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B31" s="3">
         <f t="shared" ref="B31" si="29">COUNTA(K31:VR31)</f>
         <v>0</v>
@@ -2728,7 +2899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B32" s="3">
         <f t="shared" ref="B32" si="38">COUNTA(K32:VR32)</f>
         <v>0</v>

--- a/data/2026-2027/Présences.xlsx
+++ b/data/2026-2027/Présences.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BD9386B-AA15-7241-9AE6-88E1410748FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E9612D7-DD78-6040-9A22-EA8B4EA446BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{2EF0EE96-8EE0-C649-8161-B8679CB6F342}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="47">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -566,13 +566,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0866E353-69CC-CA42-AE0E-F860DC308060}">
-  <dimension ref="A1:W32"/>
+  <dimension ref="A1:AB32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:28" ht="51" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -642,18 +642,33 @@
       <c r="W1" s="6">
         <v>46227</v>
       </c>
+      <c r="X1" s="6">
+        <v>46230</v>
+      </c>
+      <c r="Y1" s="6">
+        <v>46231</v>
+      </c>
+      <c r="Z1" s="6">
+        <v>46233</v>
+      </c>
+      <c r="AA1" s="6">
+        <v>46234</v>
+      </c>
+      <c r="AB1" s="6">
+        <v>46237</v>
+      </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="3">
         <f>COUNTA(K2:VR2)</f>
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C2" s="3">
         <f>COUNTIF(K2:VR2,"P")</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D2" s="5">
         <f>COUNTIF(K2:VR2,"REP")</f>
@@ -722,14 +737,29 @@
       <c r="W2" s="3" t="s">
         <v>20</v>
       </c>
+      <c r="X2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB2" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="3">
         <f t="shared" ref="B3:B21" si="2">COUNTA(K3:VR3)</f>
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C3" s="3">
         <f t="shared" ref="C3:C21" si="3">COUNTIF(K3:VR3,"P")</f>
@@ -741,7 +771,7 @@
       </c>
       <c r="E3" s="3">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F3" s="3">
         <f t="shared" si="1"/>
@@ -802,18 +832,33 @@
       <c r="W3" s="3" t="s">
         <v>18</v>
       </c>
+      <c r="X3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AB3" s="3" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>24</v>
       </c>
       <c r="B4" s="3">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C4" s="3">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D4" s="5">
         <f t="shared" si="4"/>
@@ -882,18 +927,33 @@
       <c r="W4" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="X4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB4" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="3">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C5" s="3">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D5" s="5">
         <f t="shared" si="4"/>
@@ -962,18 +1022,33 @@
       <c r="W5" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="X5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB5" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>25</v>
       </c>
       <c r="B6" s="3">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C6" s="3">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D6" s="5">
         <f t="shared" si="4"/>
@@ -1042,18 +1117,33 @@
       <c r="W6" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="X6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB6" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>26</v>
       </c>
       <c r="B7" s="3">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C7" s="3">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D7" s="5">
         <f t="shared" si="4"/>
@@ -1065,7 +1155,7 @@
       </c>
       <c r="F7" s="3">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G7" s="3">
         <f t="shared" si="5"/>
@@ -1122,18 +1212,33 @@
       <c r="W7" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="X7" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y7" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB7" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>27</v>
       </c>
       <c r="B8" s="3">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C8" s="3">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D8" s="5">
         <f t="shared" si="4"/>
@@ -1202,18 +1307,33 @@
       <c r="W8" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="X8" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y8" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z8" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA8" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB8" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="3">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C9" s="3">
         <f t="shared" si="3"/>
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D9" s="5">
         <f t="shared" si="4"/>
@@ -1282,18 +1402,33 @@
       <c r="W9" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="X9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB9" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>28</v>
       </c>
       <c r="B10" s="3">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C10" s="3">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D10" s="5">
         <f t="shared" si="4"/>
@@ -1362,18 +1497,33 @@
       <c r="W10" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="X10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB10" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="3">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C11" s="3">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D11" s="5">
         <f t="shared" si="4"/>
@@ -1442,18 +1592,33 @@
       <c r="W11" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="X11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB11" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>13</v>
       </c>
       <c r="B12" s="3">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C12" s="3">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D12" s="5">
         <f t="shared" si="4"/>
@@ -1465,7 +1630,7 @@
       </c>
       <c r="F12" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G12" s="3">
         <f t="shared" si="5"/>
@@ -1522,18 +1687,33 @@
       <c r="W12" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="X12" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y12" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z12" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA12" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AB12" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>23</v>
       </c>
       <c r="B13" s="3">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C13" s="3">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D13" s="5">
         <f t="shared" si="4"/>
@@ -1602,18 +1782,33 @@
       <c r="W13" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="X13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB13" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>14</v>
       </c>
       <c r="B14" s="3">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C14" s="3">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D14" s="5">
         <f t="shared" si="4"/>
@@ -1682,18 +1877,33 @@
       <c r="W14" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="X14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB14" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>29</v>
       </c>
       <c r="B15" s="3">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C15" s="3">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D15" s="5">
         <f t="shared" si="4"/>
@@ -1762,18 +1972,33 @@
       <c r="W15" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="X15" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y15" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z15" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA15" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB15" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>30</v>
       </c>
       <c r="B16" s="3">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C16" s="3">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D16" s="5">
         <f t="shared" si="4"/>
@@ -1781,7 +2006,7 @@
       </c>
       <c r="E16" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F16" s="3">
         <f t="shared" si="1"/>
@@ -1842,18 +2067,33 @@
       <c r="W16" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="X16" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y16" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z16" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA16" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AB16" s="3" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>31</v>
       </c>
       <c r="B17" s="3">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C17" s="3">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D17" s="5">
         <f t="shared" si="4"/>
@@ -1922,18 +2162,33 @@
       <c r="W17" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="X17" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y17" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z17" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA17" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB17" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>21</v>
       </c>
       <c r="B18" s="3">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C18" s="3">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D18" s="5">
         <f t="shared" si="4"/>
@@ -2002,18 +2257,33 @@
       <c r="W18" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="X18" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y18" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z18" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA18" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB18" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>16</v>
       </c>
       <c r="B19" s="3">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C19" s="3">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D19" s="5">
         <f t="shared" si="4"/>
@@ -2082,18 +2352,33 @@
       <c r="W19" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="X19" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y19" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z19" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA19" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB19" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>37</v>
       </c>
       <c r="B20" s="3">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C20" s="3">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D20" s="5">
         <f t="shared" si="4"/>
@@ -2101,7 +2386,7 @@
       </c>
       <c r="E20" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F20" s="3">
         <f t="shared" si="1"/>
@@ -2162,18 +2447,33 @@
       <c r="W20" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="X20" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y20" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z20" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA20" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB20" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>32</v>
       </c>
       <c r="B21" s="3">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C21" s="3">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D21" s="5">
         <f t="shared" si="4"/>
@@ -2242,18 +2542,33 @@
       <c r="W21" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="X21" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y21" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z21" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA21" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB21" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>33</v>
       </c>
       <c r="B22" s="3">
         <f t="shared" ref="B22:B26" si="9">COUNTA(K22:VR22)</f>
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C22" s="3">
         <f t="shared" ref="C22:C26" si="10">COUNTIF(K22:VR22,"P")</f>
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D22" s="5">
         <f t="shared" si="4"/>
@@ -2322,18 +2637,33 @@
       <c r="W22" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="X22" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y22" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z22" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA22" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB22" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>34</v>
       </c>
       <c r="B23" s="3">
         <f t="shared" si="9"/>
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C23" s="3">
         <f t="shared" si="10"/>
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D23" s="5">
         <f t="shared" si="4"/>
@@ -2341,7 +2671,7 @@
       </c>
       <c r="E23" s="3">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F23" s="3">
         <f t="shared" si="1"/>
@@ -2402,18 +2732,33 @@
       <c r="W23" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="X23" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y23" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z23" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA23" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB23" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>36</v>
       </c>
       <c r="B24" s="3">
         <f t="shared" si="9"/>
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C24" s="3">
         <f t="shared" si="10"/>
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D24" s="5">
         <f t="shared" si="4"/>
@@ -2482,18 +2827,33 @@
       <c r="W24" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="X24" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y24" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z24" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA24" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB24" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>35</v>
       </c>
       <c r="B25" s="3">
         <f t="shared" si="9"/>
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C25" s="3">
         <f t="shared" si="10"/>
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D25" s="5">
         <f t="shared" si="4"/>
@@ -2505,7 +2865,7 @@
       </c>
       <c r="F25" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25" s="3">
         <f t="shared" si="5"/>
@@ -2562,14 +2922,29 @@
       <c r="W25" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="X25" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y25" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z25" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA25" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB25" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>15</v>
       </c>
       <c r="B26" s="3">
         <f t="shared" si="9"/>
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C26" s="3">
         <f t="shared" si="10"/>
@@ -2585,7 +2960,7 @@
       </c>
       <c r="F26" s="3">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G26" s="3">
         <f t="shared" si="5"/>
@@ -2642,18 +3017,33 @@
       <c r="W26" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="X26" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y26" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z26" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA26" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AB26" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>38</v>
       </c>
       <c r="B27" s="3">
         <f t="shared" ref="B27:B29" si="11">COUNTA(K27:VR27)</f>
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C27" s="3">
         <f t="shared" ref="C27:C29" si="12">COUNTIF(K27:VR27,"P")</f>
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D27" s="5">
         <f t="shared" ref="D27:D29" si="13">COUNTIF(K27:VR27,"REP")</f>
@@ -2716,18 +3106,33 @@
       <c r="W27" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="X27" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y27" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z27" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA27" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB27" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>39</v>
       </c>
       <c r="B28" s="3">
         <f t="shared" si="11"/>
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C28" s="3">
         <f t="shared" si="12"/>
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D28" s="5">
         <f t="shared" si="13"/>
@@ -2784,8 +3189,23 @@
       <c r="W28" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="X28" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y28" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z28" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA28" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB28" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B29" s="3">
         <f t="shared" si="11"/>
         <v>0</v>
@@ -2823,7 +3243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B30" s="3">
         <f t="shared" ref="B30" si="20">COUNTA(K30:VR30)</f>
         <v>0</v>
@@ -2861,7 +3281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B31" s="3">
         <f t="shared" ref="B31" si="29">COUNTA(K31:VR31)</f>
         <v>0</v>
@@ -2899,7 +3319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B32" s="3">
         <f t="shared" ref="B32" si="38">COUNTA(K32:VR32)</f>
         <v>0</v>

--- a/data/2026-2027/Présences.xlsx
+++ b/data/2026-2027/Présences.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E9612D7-DD78-6040-9A22-EA8B4EA446BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DB5953C-3FE5-5B49-B421-3472257640AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{2EF0EE96-8EE0-C649-8161-B8679CB6F342}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="47">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -566,13 +566,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0866E353-69CC-CA42-AE0E-F860DC308060}">
-  <dimension ref="A1:AB32"/>
+  <dimension ref="A1:AC32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:29" ht="51" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -657,18 +657,21 @@
       <c r="AB1" s="6">
         <v>46237</v>
       </c>
+      <c r="AC1" s="6">
+        <v>46238</v>
+      </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="3">
         <f>COUNTA(K2:VR2)</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" s="3">
         <f>COUNTIF(K2:VR2,"P")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" s="5">
         <f>COUNTIF(K2:VR2,"REP")</f>
@@ -752,14 +755,17 @@
       <c r="AB2" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AC2" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="3">
         <f t="shared" ref="B3:B21" si="2">COUNTA(K3:VR3)</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" s="3">
         <f t="shared" ref="C3:C21" si="3">COUNTIF(K3:VR3,"P")</f>
@@ -771,7 +777,7 @@
       </c>
       <c r="E3" s="3">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F3" s="3">
         <f t="shared" si="1"/>
@@ -847,18 +853,21 @@
       <c r="AB3" s="3" t="s">
         <v>18</v>
       </c>
+      <c r="AC3" s="3" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>24</v>
       </c>
       <c r="B4" s="3">
         <f t="shared" si="2"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" s="3">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D4" s="5">
         <f t="shared" si="4"/>
@@ -942,18 +951,21 @@
       <c r="AB4" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AC4" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="3">
         <f t="shared" si="2"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C5" s="3">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D5" s="5">
         <f t="shared" si="4"/>
@@ -1037,18 +1049,21 @@
       <c r="AB5" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AC5" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>25</v>
       </c>
       <c r="B6" s="3">
         <f t="shared" si="2"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" s="3">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D6" s="5">
         <f t="shared" si="4"/>
@@ -1132,18 +1147,21 @@
       <c r="AB6" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AC6" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>26</v>
       </c>
       <c r="B7" s="3">
         <f t="shared" si="2"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" s="3">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D7" s="5">
         <f t="shared" si="4"/>
@@ -1227,18 +1245,21 @@
       <c r="AB7" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AC7" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>27</v>
       </c>
       <c r="B8" s="3">
         <f t="shared" si="2"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8" s="3">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D8" s="5">
         <f t="shared" si="4"/>
@@ -1322,18 +1343,21 @@
       <c r="AB8" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AC8" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="3">
         <f t="shared" si="2"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C9" s="3">
         <f t="shared" si="3"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D9" s="5">
         <f t="shared" si="4"/>
@@ -1417,18 +1441,21 @@
       <c r="AB9" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AC9" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>28</v>
       </c>
       <c r="B10" s="3">
         <f t="shared" si="2"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C10" s="3">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D10" s="5">
         <f t="shared" si="4"/>
@@ -1512,18 +1539,21 @@
       <c r="AB10" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AC10" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="3">
         <f t="shared" si="2"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C11" s="3">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D11" s="5">
         <f t="shared" si="4"/>
@@ -1607,18 +1637,21 @@
       <c r="AB11" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AC11" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>13</v>
       </c>
       <c r="B12" s="3">
         <f t="shared" si="2"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" s="3">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D12" s="5">
         <f t="shared" si="4"/>
@@ -1702,18 +1735,21 @@
       <c r="AB12" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AC12" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>23</v>
       </c>
       <c r="B13" s="3">
         <f t="shared" si="2"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C13" s="3">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D13" s="5">
         <f t="shared" si="4"/>
@@ -1797,18 +1833,21 @@
       <c r="AB13" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AC13" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>14</v>
       </c>
       <c r="B14" s="3">
         <f t="shared" si="2"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C14" s="3">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D14" s="5">
         <f t="shared" si="4"/>
@@ -1892,18 +1931,21 @@
       <c r="AB14" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AC14" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>29</v>
       </c>
       <c r="B15" s="3">
         <f t="shared" si="2"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C15" s="3">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D15" s="5">
         <f t="shared" si="4"/>
@@ -1987,14 +2029,17 @@
       <c r="AB15" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AC15" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>30</v>
       </c>
       <c r="B16" s="3">
         <f t="shared" si="2"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C16" s="3">
         <f t="shared" si="3"/>
@@ -2006,7 +2051,7 @@
       </c>
       <c r="E16" s="3">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F16" s="3">
         <f t="shared" si="1"/>
@@ -2082,18 +2127,21 @@
       <c r="AB16" s="3" t="s">
         <v>18</v>
       </c>
+      <c r="AC16" s="3" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>31</v>
       </c>
       <c r="B17" s="3">
         <f t="shared" si="2"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C17" s="3">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D17" s="5">
         <f t="shared" si="4"/>
@@ -2177,18 +2225,21 @@
       <c r="AB17" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AC17" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>21</v>
       </c>
       <c r="B18" s="3">
         <f t="shared" si="2"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C18" s="3">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D18" s="5">
         <f t="shared" si="4"/>
@@ -2272,18 +2323,21 @@
       <c r="AB18" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AC18" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="19" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>16</v>
       </c>
       <c r="B19" s="3">
         <f t="shared" si="2"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C19" s="3">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D19" s="5">
         <f t="shared" si="4"/>
@@ -2367,18 +2421,21 @@
       <c r="AB19" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AC19" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="20" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>37</v>
       </c>
       <c r="B20" s="3">
         <f t="shared" si="2"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C20" s="3">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D20" s="5">
         <f t="shared" si="4"/>
@@ -2462,18 +2519,21 @@
       <c r="AB20" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AC20" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="21" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>32</v>
       </c>
       <c r="B21" s="3">
         <f t="shared" si="2"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C21" s="3">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D21" s="5">
         <f t="shared" si="4"/>
@@ -2557,18 +2617,21 @@
       <c r="AB21" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AC21" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="22" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>33</v>
       </c>
       <c r="B22" s="3">
         <f t="shared" ref="B22:B26" si="9">COUNTA(K22:VR22)</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C22" s="3">
         <f t="shared" ref="C22:C26" si="10">COUNTIF(K22:VR22,"P")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D22" s="5">
         <f t="shared" si="4"/>
@@ -2652,18 +2715,21 @@
       <c r="AB22" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AC22" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="23" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>34</v>
       </c>
       <c r="B23" s="3">
         <f t="shared" si="9"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C23" s="3">
         <f t="shared" si="10"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D23" s="5">
         <f t="shared" si="4"/>
@@ -2747,18 +2813,21 @@
       <c r="AB23" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AC23" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="24" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>36</v>
       </c>
       <c r="B24" s="3">
         <f t="shared" si="9"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C24" s="3">
         <f t="shared" si="10"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D24" s="5">
         <f t="shared" si="4"/>
@@ -2842,18 +2911,21 @@
       <c r="AB24" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AC24" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="25" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>35</v>
       </c>
       <c r="B25" s="3">
         <f t="shared" si="9"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C25" s="3">
         <f t="shared" si="10"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D25" s="5">
         <f t="shared" si="4"/>
@@ -2937,14 +3009,17 @@
       <c r="AB25" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AC25" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="26" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>15</v>
       </c>
       <c r="B26" s="3">
         <f t="shared" si="9"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C26" s="3">
         <f t="shared" si="10"/>
@@ -2960,7 +3035,7 @@
       </c>
       <c r="F26" s="3">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G26" s="3">
         <f t="shared" si="5"/>
@@ -3032,18 +3107,21 @@
       <c r="AB26" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="AC26" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="27" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>38</v>
       </c>
       <c r="B27" s="3">
         <f t="shared" ref="B27:B29" si="11">COUNTA(K27:VR27)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C27" s="3">
         <f t="shared" ref="C27:C29" si="12">COUNTIF(K27:VR27,"P")</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D27" s="5">
         <f t="shared" ref="D27:D29" si="13">COUNTIF(K27:VR27,"REP")</f>
@@ -3121,18 +3199,21 @@
       <c r="AB27" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AC27" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="28" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>39</v>
       </c>
       <c r="B28" s="3">
         <f t="shared" si="11"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C28" s="3">
         <f t="shared" si="12"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D28" s="5">
         <f t="shared" si="13"/>
@@ -3204,8 +3285,11 @@
       <c r="AB28" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AC28" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="29" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B29" s="3">
         <f t="shared" si="11"/>
         <v>0</v>
@@ -3243,7 +3327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B30" s="3">
         <f t="shared" ref="B30" si="20">COUNTA(K30:VR30)</f>
         <v>0</v>
@@ -3281,7 +3365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B31" s="3">
         <f t="shared" ref="B31" si="29">COUNTA(K31:VR31)</f>
         <v>0</v>
@@ -3319,7 +3403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B32" s="3">
         <f t="shared" ref="B32" si="38">COUNTA(K32:VR32)</f>
         <v>0</v>

--- a/data/2026-2027/Présences.xlsx
+++ b/data/2026-2027/Présences.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DB5953C-3FE5-5B49-B421-3472257640AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1373FBAA-93AE-BE46-B2DD-BB7BC3E6E40A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{2EF0EE96-8EE0-C649-8161-B8679CB6F342}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="48">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -177,6 +177,9 @@
   </si>
   <si>
     <t>23/07/2026 (2)</t>
+  </si>
+  <si>
+    <t>REP</t>
   </si>
 </sst>
 </file>
@@ -566,13 +569,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0866E353-69CC-CA42-AE0E-F860DC308060}">
-  <dimension ref="A1:AC32"/>
+  <dimension ref="A1:AD32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:30" ht="51" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -660,18 +663,21 @@
       <c r="AC1" s="6">
         <v>46238</v>
       </c>
+      <c r="AD1" s="6">
+        <v>46239</v>
+      </c>
     </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="3">
         <f>COUNTA(K2:VR2)</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2" s="3">
         <f>COUNTIF(K2:VR2,"P")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="5">
         <f>COUNTIF(K2:VR2,"REP")</f>
@@ -758,14 +764,17 @@
       <c r="AC2" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AD2" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="3">
         <f t="shared" ref="B3:B21" si="2">COUNTA(K3:VR3)</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C3" s="3">
         <f t="shared" ref="C3:C21" si="3">COUNTIF(K3:VR3,"P")</f>
@@ -777,7 +786,7 @@
       </c>
       <c r="E3" s="3">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F3" s="3">
         <f t="shared" si="1"/>
@@ -856,18 +865,21 @@
       <c r="AC3" s="3" t="s">
         <v>18</v>
       </c>
+      <c r="AD3" s="3" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>24</v>
       </c>
       <c r="B4" s="3">
         <f t="shared" si="2"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4" s="3">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D4" s="5">
         <f t="shared" si="4"/>
@@ -954,14 +966,17 @@
       <c r="AC4" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AD4" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="3">
         <f t="shared" si="2"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5" s="3">
         <f t="shared" si="3"/>
@@ -969,7 +984,7 @@
       </c>
       <c r="D5" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" s="3">
         <f t="shared" si="0"/>
@@ -1052,18 +1067,21 @@
       <c r="AC5" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AD5" s="3" t="s">
+        <v>47</v>
+      </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>25</v>
       </c>
       <c r="B6" s="3">
         <f t="shared" si="2"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6" s="3">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D6" s="5">
         <f t="shared" si="4"/>
@@ -1150,18 +1168,21 @@
       <c r="AC6" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AD6" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>26</v>
       </c>
       <c r="B7" s="3">
         <f t="shared" si="2"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" s="3">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D7" s="5">
         <f t="shared" si="4"/>
@@ -1248,14 +1269,17 @@
       <c r="AC7" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AD7" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>27</v>
       </c>
       <c r="B8" s="3">
         <f t="shared" si="2"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" s="3">
         <f t="shared" si="3"/>
@@ -1271,7 +1295,7 @@
       </c>
       <c r="F8" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" s="3">
         <f t="shared" si="5"/>
@@ -1346,18 +1370,21 @@
       <c r="AC8" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AD8" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="3">
         <f t="shared" si="2"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9" s="3">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D9" s="5">
         <f t="shared" si="4"/>
@@ -1444,18 +1471,21 @@
       <c r="AC9" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AD9" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>28</v>
       </c>
       <c r="B10" s="3">
         <f t="shared" si="2"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C10" s="3">
         <f t="shared" si="3"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D10" s="5">
         <f t="shared" si="4"/>
@@ -1542,18 +1572,21 @@
       <c r="AC10" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AD10" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="3">
         <f t="shared" si="2"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C11" s="3">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D11" s="5">
         <f t="shared" si="4"/>
@@ -1640,18 +1673,21 @@
       <c r="AC11" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AD11" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>13</v>
       </c>
       <c r="B12" s="3">
         <f t="shared" si="2"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C12" s="3">
         <f t="shared" si="3"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D12" s="5">
         <f t="shared" si="4"/>
@@ -1738,18 +1774,21 @@
       <c r="AC12" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AD12" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>23</v>
       </c>
       <c r="B13" s="3">
         <f t="shared" si="2"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C13" s="3">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D13" s="5">
         <f t="shared" si="4"/>
@@ -1836,18 +1875,21 @@
       <c r="AC13" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AD13" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>14</v>
       </c>
       <c r="B14" s="3">
         <f t="shared" si="2"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C14" s="3">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D14" s="5">
         <f t="shared" si="4"/>
@@ -1934,18 +1976,21 @@
       <c r="AC14" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AD14" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>29</v>
       </c>
       <c r="B15" s="3">
         <f t="shared" si="2"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C15" s="3">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D15" s="5">
         <f t="shared" si="4"/>
@@ -2032,14 +2077,17 @@
       <c r="AC15" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AD15" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>30</v>
       </c>
       <c r="B16" s="3">
         <f t="shared" si="2"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C16" s="3">
         <f t="shared" si="3"/>
@@ -2051,7 +2099,7 @@
       </c>
       <c r="E16" s="3">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F16" s="3">
         <f t="shared" si="1"/>
@@ -2130,18 +2178,21 @@
       <c r="AC16" s="3" t="s">
         <v>18</v>
       </c>
+      <c r="AD16" s="3" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="17" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>31</v>
       </c>
       <c r="B17" s="3">
         <f t="shared" si="2"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C17" s="3">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D17" s="5">
         <f t="shared" si="4"/>
@@ -2228,14 +2279,17 @@
       <c r="AC17" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AD17" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="18" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>21</v>
       </c>
       <c r="B18" s="3">
         <f t="shared" si="2"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C18" s="3">
         <f t="shared" si="3"/>
@@ -2251,7 +2305,7 @@
       </c>
       <c r="F18" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" s="3">
         <f t="shared" si="5"/>
@@ -2326,18 +2380,21 @@
       <c r="AC18" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AD18" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="19" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>16</v>
       </c>
       <c r="B19" s="3">
         <f t="shared" si="2"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C19" s="3">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D19" s="5">
         <f t="shared" si="4"/>
@@ -2424,18 +2481,21 @@
       <c r="AC19" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AD19" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="20" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>37</v>
       </c>
       <c r="B20" s="3">
         <f t="shared" si="2"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C20" s="3">
         <f t="shared" si="3"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D20" s="5">
         <f t="shared" si="4"/>
@@ -2522,18 +2582,21 @@
       <c r="AC20" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AD20" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="21" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>32</v>
       </c>
       <c r="B21" s="3">
         <f t="shared" si="2"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C21" s="3">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D21" s="5">
         <f t="shared" si="4"/>
@@ -2620,18 +2683,21 @@
       <c r="AC21" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AD21" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="22" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>33</v>
       </c>
       <c r="B22" s="3">
         <f t="shared" ref="B22:B26" si="9">COUNTA(K22:VR22)</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C22" s="3">
         <f t="shared" ref="C22:C26" si="10">COUNTIF(K22:VR22,"P")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D22" s="5">
         <f t="shared" si="4"/>
@@ -2718,18 +2784,21 @@
       <c r="AC22" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AD22" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="23" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>34</v>
       </c>
       <c r="B23" s="3">
         <f t="shared" si="9"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C23" s="3">
         <f t="shared" si="10"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D23" s="5">
         <f t="shared" si="4"/>
@@ -2816,18 +2885,21 @@
       <c r="AC23" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AD23" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="24" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>36</v>
       </c>
       <c r="B24" s="3">
         <f t="shared" si="9"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C24" s="3">
         <f t="shared" si="10"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D24" s="5">
         <f t="shared" si="4"/>
@@ -2914,18 +2986,21 @@
       <c r="AC24" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AD24" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="25" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>35</v>
       </c>
       <c r="B25" s="3">
         <f t="shared" si="9"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C25" s="3">
         <f t="shared" si="10"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D25" s="5">
         <f t="shared" si="4"/>
@@ -3012,14 +3087,17 @@
       <c r="AC25" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AD25" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="26" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>15</v>
       </c>
       <c r="B26" s="3">
         <f t="shared" si="9"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C26" s="3">
         <f t="shared" si="10"/>
@@ -3035,7 +3113,7 @@
       </c>
       <c r="F26" s="3">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G26" s="3">
         <f t="shared" si="5"/>
@@ -3110,18 +3188,21 @@
       <c r="AC26" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="AD26" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="27" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>38</v>
       </c>
       <c r="B27" s="3">
         <f t="shared" ref="B27:B29" si="11">COUNTA(K27:VR27)</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C27" s="3">
         <f t="shared" ref="C27:C29" si="12">COUNTIF(K27:VR27,"P")</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D27" s="5">
         <f t="shared" ref="D27:D29" si="13">COUNTIF(K27:VR27,"REP")</f>
@@ -3202,18 +3283,21 @@
       <c r="AC27" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AD27" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="28" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>39</v>
       </c>
       <c r="B28" s="3">
         <f t="shared" si="11"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C28" s="3">
         <f t="shared" si="12"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D28" s="5">
         <f t="shared" si="13"/>
@@ -3288,8 +3372,11 @@
       <c r="AC28" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AD28" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="29" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B29" s="3">
         <f t="shared" si="11"/>
         <v>0</v>
@@ -3327,7 +3414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B30" s="3">
         <f t="shared" ref="B30" si="20">COUNTA(K30:VR30)</f>
         <v>0</v>
@@ -3365,7 +3452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B31" s="3">
         <f t="shared" ref="B31" si="29">COUNTA(K31:VR31)</f>
         <v>0</v>
@@ -3403,7 +3490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B32" s="3">
         <f t="shared" ref="B32" si="38">COUNTA(K32:VR32)</f>
         <v>0</v>

--- a/data/2026-2027/Présences.xlsx
+++ b/data/2026-2027/Présences.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1373FBAA-93AE-BE46-B2DD-BB7BC3E6E40A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B3733A3-2220-4D4A-B7C0-307AE58BDCC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{2EF0EE96-8EE0-C649-8161-B8679CB6F342}"/>
   </bookViews>
@@ -664,7 +664,7 @@
         <v>46238</v>
       </c>
       <c r="AD1" s="6">
-        <v>46239</v>
+        <v>46240</v>
       </c>
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.2">

--- a/data/2026-2027/Présences.xlsx
+++ b/data/2026-2027/Présences.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B3733A3-2220-4D4A-B7C0-307AE58BDCC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{984EC385-4C41-C84A-B51E-DED279C30547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{2EF0EE96-8EE0-C649-8161-B8679CB6F342}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="48">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -569,13 +569,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0866E353-69CC-CA42-AE0E-F860DC308060}">
-  <dimension ref="A1:AD32"/>
+  <dimension ref="A1:AG32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:33" ht="51" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -666,14 +666,23 @@
       <c r="AD1" s="6">
         <v>46240</v>
       </c>
+      <c r="AE1" s="6">
+        <v>46244</v>
+      </c>
+      <c r="AF1" s="6">
+        <v>46247</v>
+      </c>
+      <c r="AG1" s="6">
+        <v>46247</v>
+      </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="3">
         <f>COUNTA(K2:VR2)</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C2" s="3">
         <f>COUNTIF(K2:VR2,"P")</f>
@@ -685,7 +694,7 @@
       </c>
       <c r="E2" s="3">
         <f t="shared" ref="E2:E26" si="0">COUNTIF(K2:VS2,"A")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F2" s="3">
         <f t="shared" ref="F2:F26" si="1">COUNTIF(K2:VT2,"B")</f>
@@ -767,18 +776,24 @@
       <c r="AD2" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AE2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AF2" s="3" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="3">
         <f t="shared" ref="B3:B21" si="2">COUNTA(K3:VR3)</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C3" s="3">
         <f t="shared" ref="C3:C21" si="3">COUNTIF(K3:VR3,"P")</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D3" s="5">
         <f t="shared" ref="D3:D26" si="4">COUNTIF(K3:VR3,"REP")</f>
@@ -868,18 +883,24 @@
       <c r="AD3" s="3" t="s">
         <v>18</v>
       </c>
+      <c r="AE3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF3" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>24</v>
       </c>
       <c r="B4" s="3">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C4" s="3">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D4" s="5">
         <f t="shared" si="4"/>
@@ -969,18 +990,24 @@
       <c r="AD4" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AE4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF4" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="3">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C5" s="3">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D5" s="5">
         <f t="shared" si="4"/>
@@ -1070,18 +1097,24 @@
       <c r="AD5" s="3" t="s">
         <v>47</v>
       </c>
+      <c r="AE5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF5" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>25</v>
       </c>
       <c r="B6" s="3">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C6" s="3">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D6" s="5">
         <f t="shared" si="4"/>
@@ -1171,18 +1204,24 @@
       <c r="AD6" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AE6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF6" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>26</v>
       </c>
       <c r="B7" s="3">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C7" s="3">
         <f t="shared" si="3"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D7" s="5">
         <f t="shared" si="4"/>
@@ -1272,14 +1311,20 @@
       <c r="AD7" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AE7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF7" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>27</v>
       </c>
       <c r="B8" s="3">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C8" s="3">
         <f t="shared" si="3"/>
@@ -1295,7 +1340,7 @@
       </c>
       <c r="F8" s="3">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G8" s="3">
         <f t="shared" si="5"/>
@@ -1373,18 +1418,24 @@
       <c r="AD8" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="AE8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF8" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="3">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C9" s="3">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D9" s="5">
         <f t="shared" si="4"/>
@@ -1474,18 +1525,24 @@
       <c r="AD9" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AE9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF9" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>28</v>
       </c>
       <c r="B10" s="3">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C10" s="3">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D10" s="5">
         <f t="shared" si="4"/>
@@ -1575,18 +1632,24 @@
       <c r="AD10" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AE10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF10" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="3">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C11" s="3">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D11" s="5">
         <f t="shared" si="4"/>
@@ -1676,18 +1739,24 @@
       <c r="AD11" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AE11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF11" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>13</v>
       </c>
       <c r="B12" s="3">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C12" s="3">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D12" s="5">
         <f t="shared" si="4"/>
@@ -1699,7 +1768,7 @@
       </c>
       <c r="F12" s="3">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G12" s="3">
         <f t="shared" si="5"/>
@@ -1711,7 +1780,7 @@
       </c>
       <c r="I12" s="3">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J12" s="3">
         <f t="shared" si="8"/>
@@ -1775,20 +1844,26 @@
         <v>7</v>
       </c>
       <c r="AD12" s="3" t="s">
-        <v>7</v>
+        <v>44</v>
+      </c>
+      <c r="AE12" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="AF12" s="3" t="s">
+        <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>23</v>
       </c>
       <c r="B13" s="3">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C13" s="3">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D13" s="5">
         <f t="shared" si="4"/>
@@ -1878,14 +1953,20 @@
       <c r="AD13" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AE13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF13" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>14</v>
       </c>
       <c r="B14" s="3">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C14" s="3">
         <f t="shared" si="3"/>
@@ -1901,7 +1982,7 @@
       </c>
       <c r="F14" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G14" s="3">
         <f t="shared" si="5"/>
@@ -1979,18 +2060,24 @@
       <c r="AD14" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AE14" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF14" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>29</v>
       </c>
       <c r="B15" s="3">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C15" s="3">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D15" s="5">
         <f t="shared" si="4"/>
@@ -2080,18 +2167,24 @@
       <c r="AD15" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AE15" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF15" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>30</v>
       </c>
       <c r="B16" s="3">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C16" s="3">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D16" s="5">
         <f t="shared" si="4"/>
@@ -2181,18 +2274,24 @@
       <c r="AD16" s="3" t="s">
         <v>18</v>
       </c>
+      <c r="AE16" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF16" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="17" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>31</v>
       </c>
       <c r="B17" s="3">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C17" s="3">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D17" s="5">
         <f t="shared" si="4"/>
@@ -2282,18 +2381,24 @@
       <c r="AD17" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AE17" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF17" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="18" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>21</v>
       </c>
       <c r="B18" s="3">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C18" s="3">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D18" s="5">
         <f t="shared" si="4"/>
@@ -2305,7 +2410,7 @@
       </c>
       <c r="F18" s="3">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G18" s="3">
         <f t="shared" si="5"/>
@@ -2383,18 +2488,24 @@
       <c r="AD18" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="AE18" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF18" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="19" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>16</v>
       </c>
       <c r="B19" s="3">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C19" s="3">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D19" s="5">
         <f t="shared" si="4"/>
@@ -2484,14 +2595,20 @@
       <c r="AD19" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AE19" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF19" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="20" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>37</v>
       </c>
       <c r="B20" s="3">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C20" s="3">
         <f t="shared" si="3"/>
@@ -2503,11 +2620,11 @@
       </c>
       <c r="E20" s="3">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F20" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" s="3">
         <f t="shared" si="5"/>
@@ -2585,18 +2702,24 @@
       <c r="AD20" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AE20" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AF20" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="21" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>32</v>
       </c>
       <c r="B21" s="3">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C21" s="3">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D21" s="5">
         <f t="shared" si="4"/>
@@ -2686,18 +2809,24 @@
       <c r="AD21" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AE21" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF21" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="22" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>33</v>
       </c>
       <c r="B22" s="3">
         <f t="shared" ref="B22:B26" si="9">COUNTA(K22:VR22)</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C22" s="3">
         <f t="shared" ref="C22:C26" si="10">COUNTIF(K22:VR22,"P")</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D22" s="5">
         <f t="shared" si="4"/>
@@ -2787,18 +2916,24 @@
       <c r="AD22" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AE22" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF22" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="23" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>34</v>
       </c>
       <c r="B23" s="3">
         <f t="shared" si="9"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C23" s="3">
         <f t="shared" si="10"/>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D23" s="5">
         <f t="shared" si="4"/>
@@ -2888,18 +3023,24 @@
       <c r="AD23" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AE23" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF23" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="24" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>36</v>
       </c>
       <c r="B24" s="3">
         <f t="shared" si="9"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C24" s="3">
         <f t="shared" si="10"/>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D24" s="5">
         <f t="shared" si="4"/>
@@ -2989,18 +3130,24 @@
       <c r="AD24" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AE24" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF24" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="25" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>35</v>
       </c>
       <c r="B25" s="3">
         <f t="shared" si="9"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C25" s="3">
         <f t="shared" si="10"/>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D25" s="5">
         <f t="shared" si="4"/>
@@ -3090,18 +3237,24 @@
       <c r="AD25" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AE25" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF25" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="26" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>15</v>
       </c>
       <c r="B26" s="3">
         <f t="shared" si="9"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C26" s="3">
         <f t="shared" si="10"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D26" s="5">
         <f t="shared" si="4"/>
@@ -3191,18 +3344,24 @@
       <c r="AD26" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="AE26" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF26" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="27" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>38</v>
       </c>
       <c r="B27" s="3">
         <f t="shared" ref="B27:B29" si="11">COUNTA(K27:VR27)</f>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C27" s="3">
         <f t="shared" ref="C27:C29" si="12">COUNTIF(K27:VR27,"P")</f>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D27" s="5">
         <f t="shared" ref="D27:D29" si="13">COUNTIF(K27:VR27,"REP")</f>
@@ -3286,18 +3445,24 @@
       <c r="AD27" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AE27" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF27" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="28" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>39</v>
       </c>
       <c r="B28" s="3">
         <f t="shared" si="11"/>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C28" s="3">
         <f t="shared" si="12"/>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D28" s="5">
         <f t="shared" si="13"/>
@@ -3375,8 +3540,14 @@
       <c r="AD28" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AE28" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF28" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="29" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B29" s="3">
         <f t="shared" si="11"/>
         <v>0</v>
@@ -3414,7 +3585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B30" s="3">
         <f t="shared" ref="B30" si="20">COUNTA(K30:VR30)</f>
         <v>0</v>
@@ -3452,7 +3623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B31" s="3">
         <f t="shared" ref="B31" si="29">COUNTA(K31:VR31)</f>
         <v>0</v>
@@ -3490,7 +3661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B32" s="3">
         <f t="shared" ref="B32" si="38">COUNTA(K32:VR32)</f>
         <v>0</v>

--- a/data/2026-2027/Présences.xlsx
+++ b/data/2026-2027/Présences.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{984EC385-4C41-C84A-B51E-DED279C30547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B5EF82A-1FB8-ED45-80E7-98B583BA784F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{2EF0EE96-8EE0-C649-8161-B8679CB6F342}"/>
   </bookViews>
@@ -672,9 +672,7 @@
       <c r="AF1" s="6">
         <v>46247</v>
       </c>
-      <c r="AG1" s="6">
-        <v>46247</v>
-      </c>
+      <c r="AG1" s="6"/>
     </row>
     <row r="2" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A2" t="s">

--- a/data/2026-2027/Présences.xlsx
+++ b/data/2026-2027/Présences.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B5EF82A-1FB8-ED45-80E7-98B583BA784F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D82A4C54-F348-B14B-8144-A1E3EEB93E91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{2EF0EE96-8EE0-C649-8161-B8679CB6F342}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="661" uniqueCount="50">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -180,6 +180,12 @@
   </si>
   <si>
     <t>REP</t>
+  </si>
+  <si>
+    <t>Brian Chevreuil</t>
+  </si>
+  <si>
+    <t>Marc Thomas</t>
   </si>
 </sst>
 </file>
@@ -672,7 +678,9 @@
       <c r="AF1" s="6">
         <v>46247</v>
       </c>
-      <c r="AG1" s="6"/>
+      <c r="AG1" s="6">
+        <v>46252</v>
+      </c>
     </row>
     <row r="2" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
@@ -680,7 +688,7 @@
       </c>
       <c r="B2" s="3">
         <f>COUNTA(K2:VR2)</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" s="3">
         <f>COUNTIF(K2:VR2,"P")</f>
@@ -692,7 +700,7 @@
       </c>
       <c r="E2" s="3">
         <f t="shared" ref="E2:E26" si="0">COUNTIF(K2:VS2,"A")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" s="3">
         <f t="shared" ref="F2:F26" si="1">COUNTIF(K2:VT2,"B")</f>
@@ -778,6 +786,9 @@
         <v>18</v>
       </c>
       <c r="AF2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AG2" s="3" t="s">
         <v>18</v>
       </c>
     </row>
@@ -787,11 +798,11 @@
       </c>
       <c r="B3" s="3">
         <f t="shared" ref="B3:B21" si="2">COUNTA(K3:VR3)</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C3" s="3">
         <f t="shared" ref="C3:C21" si="3">COUNTIF(K3:VR3,"P")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" s="5">
         <f t="shared" ref="D3:D26" si="4">COUNTIF(K3:VR3,"REP")</f>
@@ -885,6 +896,9 @@
         <v>7</v>
       </c>
       <c r="AF3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG3" s="3" t="s">
         <v>7</v>
       </c>
     </row>
@@ -894,11 +908,11 @@
       </c>
       <c r="B4" s="3">
         <f t="shared" si="2"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C4" s="3">
         <f t="shared" si="3"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D4" s="5">
         <f t="shared" si="4"/>
@@ -992,6 +1006,9 @@
         <v>7</v>
       </c>
       <c r="AF4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG4" s="3" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1001,11 +1018,11 @@
       </c>
       <c r="B5" s="3">
         <f t="shared" si="2"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" s="3">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D5" s="5">
         <f t="shared" si="4"/>
@@ -1099,6 +1116,9 @@
         <v>7</v>
       </c>
       <c r="AF5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG5" s="3" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1108,11 +1128,11 @@
       </c>
       <c r="B6" s="3">
         <f t="shared" si="2"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" s="3">
         <f t="shared" si="3"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D6" s="5">
         <f t="shared" si="4"/>
@@ -1206,6 +1226,9 @@
         <v>7</v>
       </c>
       <c r="AF6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG6" s="3" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1215,11 +1238,11 @@
       </c>
       <c r="B7" s="3">
         <f t="shared" si="2"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C7" s="3">
         <f t="shared" si="3"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D7" s="5">
         <f t="shared" si="4"/>
@@ -1313,6 +1336,9 @@
         <v>7</v>
       </c>
       <c r="AF7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG7" s="3" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1322,11 +1348,11 @@
       </c>
       <c r="B8" s="3">
         <f t="shared" si="2"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8" s="3">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D8" s="5">
         <f t="shared" si="4"/>
@@ -1421,6 +1447,9 @@
       </c>
       <c r="AF8" s="3" t="s">
         <v>44</v>
+      </c>
+      <c r="AG8" s="3" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.2">
@@ -1429,7 +1458,7 @@
       </c>
       <c r="B9" s="3">
         <f t="shared" si="2"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C9" s="3">
         <f t="shared" si="3"/>
@@ -1445,7 +1474,7 @@
       </c>
       <c r="F9" s="3">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G9" s="3">
         <f t="shared" si="5"/>
@@ -1528,6 +1557,9 @@
       </c>
       <c r="AF9" s="3" t="s">
         <v>7</v>
+      </c>
+      <c r="AG9" s="3" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.2">
@@ -1536,11 +1568,11 @@
       </c>
       <c r="B10" s="3">
         <f t="shared" si="2"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C10" s="3">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D10" s="5">
         <f t="shared" si="4"/>
@@ -1634,6 +1666,9 @@
         <v>7</v>
       </c>
       <c r="AF10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG10" s="3" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1643,11 +1678,11 @@
       </c>
       <c r="B11" s="3">
         <f t="shared" si="2"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C11" s="3">
         <f t="shared" si="3"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D11" s="5">
         <f t="shared" si="4"/>
@@ -1741,6 +1776,9 @@
         <v>7</v>
       </c>
       <c r="AF11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG11" s="3" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1750,11 +1788,11 @@
       </c>
       <c r="B12" s="3">
         <f t="shared" si="2"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C12" s="3">
         <f t="shared" si="3"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D12" s="5">
         <f t="shared" si="4"/>
@@ -1849,6 +1887,9 @@
       </c>
       <c r="AF12" s="3" t="s">
         <v>20</v>
+      </c>
+      <c r="AG12" s="3" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.2">
@@ -1857,11 +1898,11 @@
       </c>
       <c r="B13" s="3">
         <f t="shared" si="2"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C13" s="3">
         <f t="shared" si="3"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D13" s="5">
         <f t="shared" si="4"/>
@@ -1955,6 +1996,9 @@
         <v>7</v>
       </c>
       <c r="AF13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG13" s="3" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1964,7 +2008,7 @@
       </c>
       <c r="B14" s="3">
         <f t="shared" si="2"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C14" s="3">
         <f t="shared" si="3"/>
@@ -1980,7 +2024,7 @@
       </c>
       <c r="F14" s="3">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G14" s="3">
         <f t="shared" si="5"/>
@@ -2062,6 +2106,9 @@
         <v>44</v>
       </c>
       <c r="AF14" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AG14" s="3" t="s">
         <v>44</v>
       </c>
     </row>
@@ -2071,11 +2118,11 @@
       </c>
       <c r="B15" s="3">
         <f t="shared" si="2"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C15" s="3">
         <f t="shared" si="3"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D15" s="5">
         <f t="shared" si="4"/>
@@ -2169,6 +2216,9 @@
         <v>7</v>
       </c>
       <c r="AF15" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG15" s="3" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2178,11 +2228,11 @@
       </c>
       <c r="B16" s="3">
         <f t="shared" si="2"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C16" s="3">
         <f t="shared" si="3"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D16" s="5">
         <f t="shared" si="4"/>
@@ -2278,18 +2328,21 @@
       <c r="AF16" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AG16" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="17" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>31</v>
       </c>
       <c r="B17" s="3">
         <f t="shared" si="2"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C17" s="3">
         <f t="shared" si="3"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D17" s="5">
         <f t="shared" si="4"/>
@@ -2385,14 +2438,17 @@
       <c r="AF17" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AG17" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="18" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>21</v>
       </c>
       <c r="B18" s="3">
         <f t="shared" si="2"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C18" s="3">
         <f t="shared" si="3"/>
@@ -2408,7 +2464,7 @@
       </c>
       <c r="F18" s="3">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G18" s="3">
         <f t="shared" si="5"/>
@@ -2492,18 +2548,21 @@
       <c r="AF18" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="AG18" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="19" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>16</v>
       </c>
       <c r="B19" s="3">
         <f t="shared" si="2"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C19" s="3">
         <f t="shared" si="3"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D19" s="5">
         <f t="shared" si="4"/>
@@ -2599,18 +2658,21 @@
       <c r="AF19" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AG19" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="20" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>37</v>
       </c>
       <c r="B20" s="3">
         <f t="shared" si="2"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C20" s="3">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D20" s="5">
         <f t="shared" si="4"/>
@@ -2706,18 +2768,21 @@
       <c r="AF20" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="AG20" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="21" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>32</v>
       </c>
       <c r="B21" s="3">
         <f t="shared" si="2"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C21" s="3">
         <f t="shared" si="3"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D21" s="5">
         <f t="shared" si="4"/>
@@ -2813,18 +2878,21 @@
       <c r="AF21" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AG21" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="22" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>33</v>
       </c>
       <c r="B22" s="3">
         <f t="shared" ref="B22:B26" si="9">COUNTA(K22:VR22)</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C22" s="3">
         <f t="shared" ref="C22:C26" si="10">COUNTIF(K22:VR22,"P")</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D22" s="5">
         <f t="shared" si="4"/>
@@ -2920,18 +2988,21 @@
       <c r="AF22" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AG22" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="23" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>34</v>
       </c>
       <c r="B23" s="3">
         <f t="shared" si="9"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C23" s="3">
         <f t="shared" si="10"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D23" s="5">
         <f t="shared" si="4"/>
@@ -3027,18 +3098,21 @@
       <c r="AF23" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AG23" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="24" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>36</v>
       </c>
       <c r="B24" s="3">
         <f t="shared" si="9"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C24" s="3">
         <f t="shared" si="10"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D24" s="5">
         <f t="shared" si="4"/>
@@ -3134,18 +3208,21 @@
       <c r="AF24" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AG24" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="25" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>35</v>
       </c>
       <c r="B25" s="3">
         <f t="shared" si="9"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C25" s="3">
         <f t="shared" si="10"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D25" s="5">
         <f t="shared" si="4"/>
@@ -3241,18 +3318,21 @@
       <c r="AF25" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AG25" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="26" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>15</v>
       </c>
       <c r="B26" s="3">
         <f t="shared" si="9"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C26" s="3">
         <f t="shared" si="10"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D26" s="5">
         <f t="shared" si="4"/>
@@ -3348,18 +3428,21 @@
       <c r="AF26" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AG26" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="27" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>38</v>
       </c>
       <c r="B27" s="3">
         <f t="shared" ref="B27:B29" si="11">COUNTA(K27:VR27)</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C27" s="3">
         <f t="shared" ref="C27:C29" si="12">COUNTIF(K27:VR27,"P")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D27" s="5">
         <f t="shared" ref="D27:D29" si="13">COUNTIF(K27:VR27,"REP")</f>
@@ -3449,18 +3532,21 @@
       <c r="AF27" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AG27" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="28" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>39</v>
       </c>
       <c r="B28" s="3">
         <f t="shared" si="11"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C28" s="3">
         <f t="shared" si="12"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D28" s="5">
         <f t="shared" si="13"/>
@@ -3544,11 +3630,17 @@
       <c r="AF28" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AG28" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="29" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>48</v>
+      </c>
       <c r="B29" s="3">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C29" s="3">
         <f t="shared" si="12"/>
@@ -3564,7 +3656,7 @@
       </c>
       <c r="F29" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29" s="3">
         <f t="shared" si="16"/>
@@ -3582,11 +3674,17 @@
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
+      <c r="AG29" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="30" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>49</v>
+      </c>
       <c r="B30" s="3">
         <f t="shared" ref="B30" si="20">COUNTA(K30:VR30)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C30" s="3">
         <f t="shared" ref="C30" si="21">COUNTIF(K30:VR30,"P")</f>
@@ -3602,7 +3700,7 @@
       </c>
       <c r="F30" s="3">
         <f t="shared" ref="F30" si="24">COUNTIF(K30:VT30,"B")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30" s="3">
         <f t="shared" ref="G30" si="25">COUNTIF(K30:VU30,"M")</f>
@@ -3620,8 +3718,11 @@
         <f t="shared" ref="J30" si="28">COUNTIF(K30:VW30,"S")</f>
         <v>0</v>
       </c>
+      <c r="AG30" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="31" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B31" s="3">
         <f t="shared" ref="B31" si="29">COUNTA(K31:VR31)</f>
         <v>0</v>
@@ -3659,7 +3760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B32" s="3">
         <f t="shared" ref="B32" si="38">COUNTA(K32:VR32)</f>
         <v>0</v>

--- a/data/2026-2027/Présences.xlsx
+++ b/data/2026-2027/Présences.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D82A4C54-F348-B14B-8144-A1E3EEB93E91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE64A136-6976-1640-88F7-CE366193033F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{2EF0EE96-8EE0-C649-8161-B8679CB6F342}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="661" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="53">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -186,6 +186,15 @@
   </si>
   <si>
     <t>Marc Thomas</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>Sofiane Belkheir</t>
   </si>
 </sst>
 </file>
@@ -575,13 +584,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0866E353-69CC-CA42-AE0E-F860DC308060}">
-  <dimension ref="A1:AG32"/>
+  <dimension ref="A1:AJ32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" ht="51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:36" ht="51" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -681,14 +690,23 @@
       <c r="AG1" s="6">
         <v>46252</v>
       </c>
+      <c r="AH1" s="6">
+        <v>46253</v>
+      </c>
+      <c r="AI1" s="6">
+        <v>46254</v>
+      </c>
+      <c r="AJ1" s="6">
+        <v>46255</v>
+      </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="3">
         <f>COUNTA(K2:VR2)</f>
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C2" s="3">
         <f>COUNTIF(K2:VR2,"P")</f>
@@ -700,7 +718,7 @@
       </c>
       <c r="E2" s="3">
         <f t="shared" ref="E2:E26" si="0">COUNTIF(K2:VS2,"A")</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F2" s="3">
         <f t="shared" ref="F2:F26" si="1">COUNTIF(K2:VT2,"B")</f>
@@ -791,18 +809,27 @@
       <c r="AG2" s="3" t="s">
         <v>18</v>
       </c>
+      <c r="AH2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AI2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AJ2" s="3" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="3">
         <f t="shared" ref="B3:B21" si="2">COUNTA(K3:VR3)</f>
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C3" s="3">
         <f t="shared" ref="C3:C21" si="3">COUNTIF(K3:VR3,"P")</f>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D3" s="5">
         <f t="shared" ref="D3:D26" si="4">COUNTIF(K3:VR3,"REP")</f>
@@ -901,18 +928,27 @@
       <c r="AG3" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AH3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ3" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>24</v>
       </c>
       <c r="B4" s="3">
         <f t="shared" si="2"/>
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C4" s="3">
         <f t="shared" si="3"/>
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D4" s="5">
         <f t="shared" si="4"/>
@@ -1011,18 +1047,27 @@
       <c r="AG4" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AH4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ4" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="3">
         <f t="shared" si="2"/>
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C5" s="3">
         <f t="shared" si="3"/>
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D5" s="5">
         <f t="shared" si="4"/>
@@ -1121,18 +1166,27 @@
       <c r="AG5" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AH5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ5" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>25</v>
       </c>
       <c r="B6" s="3">
         <f t="shared" si="2"/>
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C6" s="3">
         <f t="shared" si="3"/>
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D6" s="5">
         <f t="shared" si="4"/>
@@ -1231,18 +1285,27 @@
       <c r="AG6" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AH6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ6" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>26</v>
       </c>
       <c r="B7" s="3">
         <f t="shared" si="2"/>
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C7" s="3">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D7" s="5">
         <f t="shared" si="4"/>
@@ -1262,7 +1325,7 @@
       </c>
       <c r="H7" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" s="3">
         <f t="shared" si="7"/>
@@ -1341,18 +1404,27 @@
       <c r="AG7" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AH7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ7" s="3" t="s">
+        <v>51</v>
+      </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>27</v>
       </c>
       <c r="B8" s="3">
         <f t="shared" si="2"/>
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C8" s="3">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D8" s="5">
         <f t="shared" si="4"/>
@@ -1451,18 +1523,27 @@
       <c r="AG8" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AH8" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI8" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ8" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="3">
         <f t="shared" si="2"/>
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C9" s="3">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D9" s="5">
         <f t="shared" si="4"/>
@@ -1486,7 +1567,7 @@
       </c>
       <c r="I9" s="3">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" s="3">
         <f t="shared" si="8"/>
@@ -1561,18 +1642,27 @@
       <c r="AG9" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="AH9" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="AI9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ9" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>28</v>
       </c>
       <c r="B10" s="3">
         <f t="shared" si="2"/>
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C10" s="3">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D10" s="5">
         <f t="shared" si="4"/>
@@ -1671,18 +1761,27 @@
       <c r="AG10" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AH10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ10" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="3">
         <f t="shared" si="2"/>
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C11" s="3">
         <f t="shared" si="3"/>
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D11" s="5">
         <f t="shared" si="4"/>
@@ -1781,18 +1880,27 @@
       <c r="AG11" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AH11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ11" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>13</v>
       </c>
       <c r="B12" s="3">
         <f t="shared" si="2"/>
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C12" s="3">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D12" s="5">
         <f t="shared" si="4"/>
@@ -1891,18 +1999,27 @@
       <c r="AG12" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AH12" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI12" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ12" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>23</v>
       </c>
       <c r="B13" s="3">
         <f t="shared" si="2"/>
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C13" s="3">
         <f t="shared" si="3"/>
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D13" s="5">
         <f t="shared" si="4"/>
@@ -2001,18 +2118,27 @@
       <c r="AG13" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AH13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ13" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>14</v>
       </c>
       <c r="B14" s="3">
         <f t="shared" si="2"/>
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C14" s="3">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D14" s="5">
         <f t="shared" si="4"/>
@@ -2111,18 +2237,27 @@
       <c r="AG14" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="AH14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ14" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>29</v>
       </c>
       <c r="B15" s="3">
         <f t="shared" si="2"/>
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C15" s="3">
         <f t="shared" si="3"/>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D15" s="5">
         <f t="shared" si="4"/>
@@ -2142,7 +2277,7 @@
       </c>
       <c r="H15" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" s="3">
         <f t="shared" si="7"/>
@@ -2221,18 +2356,27 @@
       <c r="AG15" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AH15" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI15" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ15" s="3" t="s">
+        <v>51</v>
+      </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>30</v>
       </c>
       <c r="B16" s="3">
         <f t="shared" si="2"/>
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C16" s="3">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D16" s="5">
         <f t="shared" si="4"/>
@@ -2252,7 +2396,7 @@
       </c>
       <c r="H16" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" s="3">
         <f t="shared" si="7"/>
@@ -2331,18 +2475,27 @@
       <c r="AG16" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AH16" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI16" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ16" s="3" t="s">
+        <v>51</v>
+      </c>
     </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>31</v>
       </c>
       <c r="B17" s="3">
         <f t="shared" si="2"/>
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C17" s="3">
         <f t="shared" si="3"/>
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D17" s="5">
         <f t="shared" si="4"/>
@@ -2441,18 +2594,27 @@
       <c r="AG17" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AH17" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI17" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ17" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="18" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>21</v>
       </c>
       <c r="B18" s="3">
         <f t="shared" si="2"/>
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C18" s="3">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D18" s="5">
         <f t="shared" si="4"/>
@@ -2551,18 +2713,27 @@
       <c r="AG18" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="AH18" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI18" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ18" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="19" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>16</v>
       </c>
       <c r="B19" s="3">
         <f t="shared" si="2"/>
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C19" s="3">
         <f t="shared" si="3"/>
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D19" s="5">
         <f t="shared" si="4"/>
@@ -2661,14 +2832,23 @@
       <c r="AG19" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AH19" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI19" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ19" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="20" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>37</v>
       </c>
       <c r="B20" s="3">
         <f t="shared" si="2"/>
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C20" s="3">
         <f t="shared" si="3"/>
@@ -2688,11 +2868,11 @@
       </c>
       <c r="G20" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H20" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" s="3">
         <f t="shared" si="7"/>
@@ -2771,18 +2951,27 @@
       <c r="AG20" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AH20" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="AI20" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="AJ20" s="3" t="s">
+        <v>51</v>
+      </c>
     </row>
-    <row r="21" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>32</v>
       </c>
       <c r="B21" s="3">
         <f t="shared" si="2"/>
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C21" s="3">
         <f t="shared" si="3"/>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D21" s="5">
         <f t="shared" si="4"/>
@@ -2802,7 +2991,7 @@
       </c>
       <c r="H21" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" s="3">
         <f t="shared" si="7"/>
@@ -2881,18 +3070,27 @@
       <c r="AG21" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AH21" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI21" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ21" s="3" t="s">
+        <v>51</v>
+      </c>
     </row>
-    <row r="22" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>33</v>
       </c>
       <c r="B22" s="3">
         <f t="shared" ref="B22:B26" si="9">COUNTA(K22:VR22)</f>
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C22" s="3">
         <f t="shared" ref="C22:C26" si="10">COUNTIF(K22:VR22,"P")</f>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D22" s="5">
         <f t="shared" si="4"/>
@@ -2912,7 +3110,7 @@
       </c>
       <c r="H22" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" s="3">
         <f t="shared" si="7"/>
@@ -2991,18 +3189,27 @@
       <c r="AG22" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AH22" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI22" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ22" s="3" t="s">
+        <v>51</v>
+      </c>
     </row>
-    <row r="23" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>34</v>
       </c>
       <c r="B23" s="3">
         <f t="shared" si="9"/>
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C23" s="3">
         <f t="shared" si="10"/>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D23" s="5">
         <f t="shared" si="4"/>
@@ -3022,7 +3229,7 @@
       </c>
       <c r="H23" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" s="3">
         <f t="shared" si="7"/>
@@ -3101,18 +3308,27 @@
       <c r="AG23" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AH23" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI23" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ23" s="3" t="s">
+        <v>51</v>
+      </c>
     </row>
-    <row r="24" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>36</v>
       </c>
       <c r="B24" s="3">
         <f t="shared" si="9"/>
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C24" s="3">
         <f t="shared" si="10"/>
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D24" s="5">
         <f t="shared" si="4"/>
@@ -3211,14 +3427,23 @@
       <c r="AG24" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AH24" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI24" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ24" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="25" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>35</v>
       </c>
       <c r="B25" s="3">
         <f t="shared" si="9"/>
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C25" s="3">
         <f t="shared" si="10"/>
@@ -3234,7 +3459,7 @@
       </c>
       <c r="F25" s="3">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G25" s="3">
         <f t="shared" si="5"/>
@@ -3321,18 +3546,27 @@
       <c r="AG25" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AH25" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AI25" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AJ25" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="26" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>15</v>
       </c>
       <c r="B26" s="3">
         <f t="shared" si="9"/>
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C26" s="3">
         <f t="shared" si="10"/>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D26" s="5">
         <f t="shared" si="4"/>
@@ -3431,18 +3665,27 @@
       <c r="AG26" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AH26" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI26" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ26" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="27" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>38</v>
       </c>
       <c r="B27" s="3">
         <f t="shared" ref="B27:B29" si="11">COUNTA(K27:VR27)</f>
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C27" s="3">
         <f t="shared" ref="C27:C29" si="12">COUNTIF(K27:VR27,"P")</f>
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D27" s="5">
         <f t="shared" ref="D27:D29" si="13">COUNTIF(K27:VR27,"REP")</f>
@@ -3535,18 +3778,27 @@
       <c r="AG27" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AH27" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI27" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ27" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="28" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>39</v>
       </c>
       <c r="B28" s="3">
         <f t="shared" si="11"/>
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C28" s="3">
         <f t="shared" si="12"/>
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D28" s="5">
         <f t="shared" si="13"/>
@@ -3633,14 +3885,23 @@
       <c r="AG28" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AH28" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI28" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ28" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="29" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>48</v>
       </c>
       <c r="B29" s="3">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C29" s="3">
         <f t="shared" si="12"/>
@@ -3656,7 +3917,7 @@
       </c>
       <c r="F29" s="3">
         <f t="shared" si="15"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G29" s="3">
         <f t="shared" si="16"/>
@@ -3677,14 +3938,23 @@
       <c r="AG29" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="AH29" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AI29" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AJ29" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="30" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>49</v>
       </c>
       <c r="B30" s="3">
         <f t="shared" ref="B30" si="20">COUNTA(K30:VR30)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C30" s="3">
         <f t="shared" ref="C30" si="21">COUNTIF(K30:VR30,"P")</f>
@@ -3712,7 +3982,7 @@
       </c>
       <c r="I30" s="3">
         <f t="shared" ref="I30" si="27">COUNTIF(K30:VW30,"RH")</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J30" s="3">
         <f t="shared" ref="J30" si="28">COUNTIF(K30:VW30,"S")</f>
@@ -3721,15 +3991,27 @@
       <c r="AG30" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="AH30" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="AI30" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="AJ30" s="3" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="31" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>52</v>
+      </c>
       <c r="B31" s="3">
         <f t="shared" ref="B31" si="29">COUNTA(K31:VR31)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C31" s="3">
         <f t="shared" ref="C31" si="30">COUNTIF(K31:VR31,"P")</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D31" s="5">
         <f t="shared" ref="D31" si="31">COUNTIF(K31:VR31,"REP")</f>
@@ -3749,7 +4031,7 @@
       </c>
       <c r="H31" s="3">
         <f t="shared" ref="H31" si="35">COUNTIF(K31:VV31,"R")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" s="3">
         <f t="shared" ref="I31" si="36">COUNTIF(K31:VW31,"RH")</f>
@@ -3759,8 +4041,20 @@
         <f t="shared" ref="J31" si="37">COUNTIF(K31:VW31,"S")</f>
         <v>0</v>
       </c>
+      <c r="AG31" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH31" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI31" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ31" s="3" t="s">
+        <v>51</v>
+      </c>
     </row>
-    <row r="32" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B32" s="3">
         <f t="shared" ref="B32" si="38">COUNTA(K32:VR32)</f>
         <v>0</v>

--- a/data/2026-2027/Présences.xlsx
+++ b/data/2026-2027/Présences.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE64A136-6976-1640-88F7-CE366193033F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F8B5432-BACB-B047-976A-8583FC8E2F39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{2EF0EE96-8EE0-C649-8161-B8679CB6F342}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="53">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -584,13 +584,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0866E353-69CC-CA42-AE0E-F860DC308060}">
-  <dimension ref="A1:AJ32"/>
+  <dimension ref="A1:AL32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:38" ht="51" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -699,14 +699,20 @@
       <c r="AJ1" s="6">
         <v>46255</v>
       </c>
+      <c r="AK1" s="6">
+        <v>46258</v>
+      </c>
+      <c r="AL1" s="6">
+        <v>46259</v>
+      </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="3">
         <f>COUNTA(K2:VR2)</f>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C2" s="3">
         <f>COUNTIF(K2:VR2,"P")</f>
@@ -718,7 +724,7 @@
       </c>
       <c r="E2" s="3">
         <f t="shared" ref="E2:E26" si="0">COUNTIF(K2:VS2,"A")</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F2" s="3">
         <f t="shared" ref="F2:F26" si="1">COUNTIF(K2:VT2,"B")</f>
@@ -818,18 +824,24 @@
       <c r="AJ2" s="3" t="s">
         <v>18</v>
       </c>
+      <c r="AK2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AL2" s="3" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="3">
         <f t="shared" ref="B3:B21" si="2">COUNTA(K3:VR3)</f>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C3" s="3">
         <f t="shared" ref="C3:C21" si="3">COUNTIF(K3:VR3,"P")</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D3" s="5">
         <f t="shared" ref="D3:D26" si="4">COUNTIF(K3:VR3,"REP")</f>
@@ -937,18 +949,24 @@
       <c r="AJ3" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AK3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL3" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>24</v>
       </c>
       <c r="B4" s="3">
         <f t="shared" si="2"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C4" s="3">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D4" s="5">
         <f t="shared" si="4"/>
@@ -1056,14 +1074,20 @@
       <c r="AJ4" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AK4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL4" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="3">
         <f t="shared" si="2"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C5" s="3">
         <f t="shared" si="3"/>
@@ -1079,7 +1103,7 @@
       </c>
       <c r="F5" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G5" s="3">
         <f t="shared" si="5"/>
@@ -1175,18 +1199,24 @@
       <c r="AJ5" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AK5" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AL5" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>25</v>
       </c>
       <c r="B6" s="3">
         <f t="shared" si="2"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C6" s="3">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D6" s="5">
         <f t="shared" si="4"/>
@@ -1294,18 +1324,24 @@
       <c r="AJ6" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AK6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL6" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>26</v>
       </c>
       <c r="B7" s="3">
         <f t="shared" si="2"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C7" s="3">
         <f t="shared" si="3"/>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D7" s="5">
         <f t="shared" si="4"/>
@@ -1413,14 +1449,20 @@
       <c r="AJ7" s="3" t="s">
         <v>51</v>
       </c>
+      <c r="AK7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL7" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>27</v>
       </c>
       <c r="B8" s="3">
         <f t="shared" si="2"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C8" s="3">
         <f t="shared" si="3"/>
@@ -1436,7 +1478,7 @@
       </c>
       <c r="F8" s="3">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G8" s="3">
         <f t="shared" si="5"/>
@@ -1532,18 +1574,24 @@
       <c r="AJ8" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AK8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AL8" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="3">
         <f t="shared" si="2"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C9" s="3">
         <f t="shared" si="3"/>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D9" s="5">
         <f t="shared" si="4"/>
@@ -1651,18 +1699,24 @@
       <c r="AJ9" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AK9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL9" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>28</v>
       </c>
       <c r="B10" s="3">
         <f t="shared" si="2"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C10" s="3">
         <f t="shared" si="3"/>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D10" s="5">
         <f t="shared" si="4"/>
@@ -1770,18 +1824,24 @@
       <c r="AJ10" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AK10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL10" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="3">
         <f t="shared" si="2"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C11" s="3">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D11" s="5">
         <f t="shared" si="4"/>
@@ -1889,18 +1949,24 @@
       <c r="AJ11" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AK11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL11" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>13</v>
       </c>
       <c r="B12" s="3">
         <f t="shared" si="2"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C12" s="3">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D12" s="5">
         <f t="shared" si="4"/>
@@ -2008,18 +2074,24 @@
       <c r="AJ12" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL12" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>23</v>
       </c>
       <c r="B13" s="3">
         <f t="shared" si="2"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C13" s="3">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D13" s="5">
         <f t="shared" si="4"/>
@@ -2127,18 +2199,24 @@
       <c r="AJ13" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AK13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL13" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>14</v>
       </c>
       <c r="B14" s="3">
         <f t="shared" si="2"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C14" s="3">
         <f t="shared" si="3"/>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D14" s="5">
         <f t="shared" si="4"/>
@@ -2246,18 +2324,24 @@
       <c r="AJ14" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AK14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL14" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>29</v>
       </c>
       <c r="B15" s="3">
         <f t="shared" si="2"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C15" s="3">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D15" s="5">
         <f t="shared" si="4"/>
@@ -2365,18 +2449,24 @@
       <c r="AJ15" s="3" t="s">
         <v>51</v>
       </c>
+      <c r="AK15" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL15" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>30</v>
       </c>
       <c r="B16" s="3">
         <f t="shared" si="2"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C16" s="3">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D16" s="5">
         <f t="shared" si="4"/>
@@ -2484,18 +2574,24 @@
       <c r="AJ16" s="3" t="s">
         <v>51</v>
       </c>
+      <c r="AK16" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL16" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="17" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>31</v>
       </c>
       <c r="B17" s="3">
         <f t="shared" si="2"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C17" s="3">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D17" s="5">
         <f t="shared" si="4"/>
@@ -2603,18 +2699,24 @@
       <c r="AJ17" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AK17" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL17" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="18" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>21</v>
       </c>
       <c r="B18" s="3">
         <f t="shared" si="2"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C18" s="3">
         <f t="shared" si="3"/>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D18" s="5">
         <f t="shared" si="4"/>
@@ -2722,18 +2824,24 @@
       <c r="AJ18" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AK18" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL18" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="19" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>16</v>
       </c>
       <c r="B19" s="3">
         <f t="shared" si="2"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C19" s="3">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D19" s="5">
         <f t="shared" si="4"/>
@@ -2841,18 +2949,24 @@
       <c r="AJ19" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AK19" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL19" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="20" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>37</v>
       </c>
       <c r="B20" s="3">
         <f t="shared" si="2"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C20" s="3">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D20" s="5">
         <f t="shared" si="4"/>
@@ -2960,18 +3074,24 @@
       <c r="AJ20" s="3" t="s">
         <v>51</v>
       </c>
+      <c r="AK20" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL20" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="21" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>32</v>
       </c>
       <c r="B21" s="3">
         <f t="shared" si="2"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C21" s="3">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D21" s="5">
         <f t="shared" si="4"/>
@@ -3079,18 +3199,24 @@
       <c r="AJ21" s="3" t="s">
         <v>51</v>
       </c>
+      <c r="AK21" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL21" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="22" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>33</v>
       </c>
       <c r="B22" s="3">
         <f t="shared" ref="B22:B26" si="9">COUNTA(K22:VR22)</f>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C22" s="3">
         <f t="shared" ref="C22:C26" si="10">COUNTIF(K22:VR22,"P")</f>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D22" s="5">
         <f t="shared" si="4"/>
@@ -3198,18 +3324,24 @@
       <c r="AJ22" s="3" t="s">
         <v>51</v>
       </c>
+      <c r="AK22" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL22" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="23" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>34</v>
       </c>
       <c r="B23" s="3">
         <f t="shared" si="9"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C23" s="3">
         <f t="shared" si="10"/>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D23" s="5">
         <f t="shared" si="4"/>
@@ -3317,18 +3449,24 @@
       <c r="AJ23" s="3" t="s">
         <v>51</v>
       </c>
+      <c r="AK23" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL23" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="24" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>36</v>
       </c>
       <c r="B24" s="3">
         <f t="shared" si="9"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C24" s="3">
         <f t="shared" si="10"/>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D24" s="5">
         <f t="shared" si="4"/>
@@ -3436,14 +3574,20 @@
       <c r="AJ24" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AK24" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL24" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="25" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>35</v>
       </c>
       <c r="B25" s="3">
         <f t="shared" si="9"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C25" s="3">
         <f t="shared" si="10"/>
@@ -3471,7 +3615,7 @@
       </c>
       <c r="I25" s="3">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J25" s="3">
         <f t="shared" si="8"/>
@@ -3555,18 +3699,24 @@
       <c r="AJ25" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="AK25" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="AL25" s="3" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="26" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>15</v>
       </c>
       <c r="B26" s="3">
         <f t="shared" si="9"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C26" s="3">
         <f t="shared" si="10"/>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D26" s="5">
         <f t="shared" si="4"/>
@@ -3674,18 +3824,24 @@
       <c r="AJ26" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AK26" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL26" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="27" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>38</v>
       </c>
       <c r="B27" s="3">
         <f t="shared" ref="B27:B29" si="11">COUNTA(K27:VR27)</f>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C27" s="3">
         <f t="shared" ref="C27:C29" si="12">COUNTIF(K27:VR27,"P")</f>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D27" s="5">
         <f t="shared" ref="D27:D29" si="13">COUNTIF(K27:VR27,"REP")</f>
@@ -3787,18 +3943,24 @@
       <c r="AJ27" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AK27" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL27" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="28" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>39</v>
       </c>
       <c r="B28" s="3">
         <f t="shared" si="11"/>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C28" s="3">
         <f t="shared" si="12"/>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D28" s="5">
         <f t="shared" si="13"/>
@@ -3894,18 +4056,24 @@
       <c r="AJ28" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AK28" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL28" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="29" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>48</v>
       </c>
       <c r="B29" s="3">
         <f t="shared" si="11"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C29" s="3">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D29" s="5">
         <f t="shared" si="13"/>
@@ -3947,18 +4115,24 @@
       <c r="AJ29" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="AK29" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL29" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="30" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>49</v>
       </c>
       <c r="B30" s="3">
         <f t="shared" ref="B30" si="20">COUNTA(K30:VR30)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C30" s="3">
         <f t="shared" ref="C30" si="21">COUNTIF(K30:VR30,"P")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D30" s="5">
         <f t="shared" ref="D30" si="22">COUNTIF(K30:VR30,"REP")</f>
@@ -3982,7 +4156,7 @@
       </c>
       <c r="I30" s="3">
         <f t="shared" ref="I30" si="27">COUNTIF(K30:VW30,"RH")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J30" s="3">
         <f t="shared" ref="J30" si="28">COUNTIF(K30:VW30,"S")</f>
@@ -4000,18 +4174,24 @@
       <c r="AJ30" s="3" t="s">
         <v>20</v>
       </c>
+      <c r="AK30" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL30" s="3" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="31" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>52</v>
       </c>
       <c r="B31" s="3">
         <f t="shared" ref="B31" si="29">COUNTA(K31:VR31)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C31" s="3">
         <f t="shared" ref="C31" si="30">COUNTIF(K31:VR31,"P")</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D31" s="5">
         <f t="shared" ref="D31" si="31">COUNTIF(K31:VR31,"REP")</f>
@@ -4053,8 +4233,14 @@
       <c r="AJ31" s="3" t="s">
         <v>51</v>
       </c>
+      <c r="AK31" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL31" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="32" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B32" s="3">
         <f t="shared" ref="B32" si="38">COUNTA(K32:VR32)</f>
         <v>0</v>

--- a/data/2026-2027/Présences.xlsx
+++ b/data/2026-2027/Présences.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F8B5432-BACB-B047-976A-8583FC8E2F39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FB6ECBC-A85F-CF4D-BA28-0DE3CE13F7B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{2EF0EE96-8EE0-C649-8161-B8679CB6F342}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="53">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -584,13 +584,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0866E353-69CC-CA42-AE0E-F860DC308060}">
-  <dimension ref="A1:AL32"/>
+  <dimension ref="A1:AN32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" ht="51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:40" ht="51" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -705,14 +705,20 @@
       <c r="AL1" s="6">
         <v>46259</v>
       </c>
+      <c r="AM1" s="6">
+        <v>46260</v>
+      </c>
+      <c r="AN1" s="6">
+        <v>46261</v>
+      </c>
     </row>
-    <row r="2" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="3">
         <f>COUNTA(K2:VR2)</f>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C2" s="3">
         <f>COUNTIF(K2:VR2,"P")</f>
@@ -724,7 +730,7 @@
       </c>
       <c r="E2" s="3">
         <f t="shared" ref="E2:E26" si="0">COUNTIF(K2:VS2,"A")</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F2" s="3">
         <f t="shared" ref="F2:F26" si="1">COUNTIF(K2:VT2,"B")</f>
@@ -830,18 +836,24 @@
       <c r="AL2" s="3" t="s">
         <v>18</v>
       </c>
+      <c r="AM2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AN2" s="3" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="3" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="3">
         <f t="shared" ref="B3:B21" si="2">COUNTA(K3:VR3)</f>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C3" s="3">
         <f t="shared" ref="C3:C21" si="3">COUNTIF(K3:VR3,"P")</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D3" s="5">
         <f t="shared" ref="D3:D26" si="4">COUNTIF(K3:VR3,"REP")</f>
@@ -955,18 +967,24 @@
       <c r="AL3" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AM3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AN3" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="4" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>24</v>
       </c>
       <c r="B4" s="3">
         <f t="shared" si="2"/>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C4" s="3">
         <f t="shared" si="3"/>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D4" s="5">
         <f t="shared" si="4"/>
@@ -1080,18 +1098,24 @@
       <c r="AL4" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AM4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AN4" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="3">
         <f t="shared" si="2"/>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C5" s="3">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D5" s="5">
         <f t="shared" si="4"/>
@@ -1103,7 +1127,7 @@
       </c>
       <c r="F5" s="3">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G5" s="3">
         <f t="shared" si="5"/>
@@ -1205,18 +1229,24 @@
       <c r="AL5" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="AM5" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AN5" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>25</v>
       </c>
       <c r="B6" s="3">
         <f t="shared" si="2"/>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C6" s="3">
         <f t="shared" si="3"/>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D6" s="5">
         <f t="shared" si="4"/>
@@ -1330,18 +1360,24 @@
       <c r="AL6" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AM6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AN6" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>26</v>
       </c>
       <c r="B7" s="3">
         <f t="shared" si="2"/>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C7" s="3">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D7" s="5">
         <f t="shared" si="4"/>
@@ -1455,14 +1491,20 @@
       <c r="AL7" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AM7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AN7" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>27</v>
       </c>
       <c r="B8" s="3">
         <f t="shared" si="2"/>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C8" s="3">
         <f t="shared" si="3"/>
@@ -1478,7 +1520,7 @@
       </c>
       <c r="F8" s="3">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G8" s="3">
         <f t="shared" si="5"/>
@@ -1580,18 +1622,24 @@
       <c r="AL8" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="AM8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AN8" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="3">
         <f t="shared" si="2"/>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C9" s="3">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D9" s="5">
         <f t="shared" si="4"/>
@@ -1705,18 +1753,24 @@
       <c r="AL9" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AM9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AN9" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>28</v>
       </c>
       <c r="B10" s="3">
         <f t="shared" si="2"/>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C10" s="3">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D10" s="5">
         <f t="shared" si="4"/>
@@ -1724,7 +1778,7 @@
       </c>
       <c r="E10" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="3">
         <f t="shared" si="1"/>
@@ -1830,18 +1884,24 @@
       <c r="AL10" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AM10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AN10" s="3" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="3">
         <f t="shared" si="2"/>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C11" s="3">
         <f t="shared" si="3"/>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D11" s="5">
         <f t="shared" si="4"/>
@@ -1955,18 +2015,24 @@
       <c r="AL11" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AM11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AN11" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>13</v>
       </c>
       <c r="B12" s="3">
         <f t="shared" si="2"/>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C12" s="3">
         <f t="shared" si="3"/>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D12" s="5">
         <f t="shared" si="4"/>
@@ -2080,18 +2146,24 @@
       <c r="AL12" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AN12" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>23</v>
       </c>
       <c r="B13" s="3">
         <f t="shared" si="2"/>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C13" s="3">
         <f t="shared" si="3"/>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D13" s="5">
         <f t="shared" si="4"/>
@@ -2205,18 +2277,24 @@
       <c r="AL13" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AM13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AN13" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>14</v>
       </c>
       <c r="B14" s="3">
         <f t="shared" si="2"/>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C14" s="3">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D14" s="5">
         <f t="shared" si="4"/>
@@ -2330,18 +2408,24 @@
       <c r="AL14" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AM14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AN14" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>29</v>
       </c>
       <c r="B15" s="3">
         <f t="shared" si="2"/>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C15" s="3">
         <f t="shared" si="3"/>
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D15" s="5">
         <f t="shared" si="4"/>
@@ -2455,18 +2539,24 @@
       <c r="AL15" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AM15" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AN15" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>30</v>
       </c>
       <c r="B16" s="3">
         <f t="shared" si="2"/>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C16" s="3">
         <f t="shared" si="3"/>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D16" s="5">
         <f t="shared" si="4"/>
@@ -2580,18 +2670,24 @@
       <c r="AL16" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AM16" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AN16" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="17" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>31</v>
       </c>
       <c r="B17" s="3">
         <f t="shared" si="2"/>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C17" s="3">
         <f t="shared" si="3"/>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D17" s="5">
         <f t="shared" si="4"/>
@@ -2705,18 +2801,24 @@
       <c r="AL17" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AM17" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AN17" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="18" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>21</v>
       </c>
       <c r="B18" s="3">
         <f t="shared" si="2"/>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C18" s="3">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D18" s="5">
         <f t="shared" si="4"/>
@@ -2830,18 +2932,24 @@
       <c r="AL18" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AM18" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AN18" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="19" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>16</v>
       </c>
       <c r="B19" s="3">
         <f t="shared" si="2"/>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C19" s="3">
         <f t="shared" si="3"/>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D19" s="5">
         <f t="shared" si="4"/>
@@ -2955,18 +3063,24 @@
       <c r="AL19" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AM19" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AN19" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="20" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>37</v>
       </c>
       <c r="B20" s="3">
         <f t="shared" si="2"/>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C20" s="3">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D20" s="5">
         <f t="shared" si="4"/>
@@ -3080,18 +3194,24 @@
       <c r="AL20" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AM20" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AN20" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="21" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>32</v>
       </c>
       <c r="B21" s="3">
         <f t="shared" si="2"/>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C21" s="3">
         <f t="shared" si="3"/>
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D21" s="5">
         <f t="shared" si="4"/>
@@ -3205,18 +3325,24 @@
       <c r="AL21" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AM21" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AN21" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="22" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>33</v>
       </c>
       <c r="B22" s="3">
         <f t="shared" ref="B22:B26" si="9">COUNTA(K22:VR22)</f>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C22" s="3">
         <f t="shared" ref="C22:C26" si="10">COUNTIF(K22:VR22,"P")</f>
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D22" s="5">
         <f t="shared" si="4"/>
@@ -3330,18 +3456,24 @@
       <c r="AL22" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AM22" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AN22" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="23" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>34</v>
       </c>
       <c r="B23" s="3">
         <f t="shared" si="9"/>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C23" s="3">
         <f t="shared" si="10"/>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D23" s="5">
         <f t="shared" si="4"/>
@@ -3455,18 +3587,24 @@
       <c r="AL23" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AM23" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AN23" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="24" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>36</v>
       </c>
       <c r="B24" s="3">
         <f t="shared" si="9"/>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C24" s="3">
         <f t="shared" si="10"/>
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D24" s="5">
         <f t="shared" si="4"/>
@@ -3580,18 +3718,24 @@
       <c r="AL24" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AM24" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AN24" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="25" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>35</v>
       </c>
       <c r="B25" s="3">
         <f t="shared" si="9"/>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C25" s="3">
         <f t="shared" si="10"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D25" s="5">
         <f t="shared" si="4"/>
@@ -3705,18 +3849,24 @@
       <c r="AL25" s="3" t="s">
         <v>20</v>
       </c>
+      <c r="AM25" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AN25" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="26" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>15</v>
       </c>
       <c r="B26" s="3">
         <f t="shared" si="9"/>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C26" s="3">
         <f t="shared" si="10"/>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D26" s="5">
         <f t="shared" si="4"/>
@@ -3830,22 +3980,28 @@
       <c r="AL26" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AM26" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AN26" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="27" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>38</v>
       </c>
       <c r="B27" s="3">
         <f t="shared" ref="B27:B29" si="11">COUNTA(K27:VR27)</f>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C27" s="3">
         <f t="shared" ref="C27:C29" si="12">COUNTIF(K27:VR27,"P")</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D27" s="5">
         <f t="shared" ref="D27:D29" si="13">COUNTIF(K27:VR27,"REP")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27" s="3">
         <f t="shared" ref="E27:E29" si="14">COUNTIF(K27:VS27,"A")</f>
@@ -3949,18 +4105,24 @@
       <c r="AL27" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AM27" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AN27" s="3" t="s">
+        <v>47</v>
+      </c>
     </row>
-    <row r="28" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>39</v>
       </c>
       <c r="B28" s="3">
         <f t="shared" si="11"/>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C28" s="3">
         <f t="shared" si="12"/>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D28" s="5">
         <f t="shared" si="13"/>
@@ -4062,18 +4224,24 @@
       <c r="AL28" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AM28" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AN28" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="29" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>48</v>
       </c>
       <c r="B29" s="3">
         <f t="shared" si="11"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C29" s="3">
         <f t="shared" si="12"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D29" s="5">
         <f t="shared" si="13"/>
@@ -4081,7 +4249,7 @@
       </c>
       <c r="E29" s="3">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29" s="3">
         <f t="shared" si="15"/>
@@ -4121,18 +4289,24 @@
       <c r="AL29" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AM29" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AN29" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="30" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>49</v>
       </c>
       <c r="B30" s="3">
         <f t="shared" ref="B30" si="20">COUNTA(K30:VR30)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C30" s="3">
         <f t="shared" ref="C30" si="21">COUNTIF(K30:VR30,"P")</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D30" s="5">
         <f t="shared" ref="D30" si="22">COUNTIF(K30:VR30,"REP")</f>
@@ -4180,18 +4354,24 @@
       <c r="AL30" s="3" t="s">
         <v>20</v>
       </c>
+      <c r="AM30" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AN30" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="31" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>52</v>
       </c>
       <c r="B31" s="3">
         <f t="shared" ref="B31" si="29">COUNTA(K31:VR31)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C31" s="3">
         <f t="shared" ref="C31" si="30">COUNTIF(K31:VR31,"P")</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D31" s="5">
         <f t="shared" ref="D31" si="31">COUNTIF(K31:VR31,"REP")</f>
@@ -4239,8 +4419,14 @@
       <c r="AL31" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AM31" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AN31" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="32" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:40" x14ac:dyDescent="0.2">
       <c r="B32" s="3">
         <f t="shared" ref="B32" si="38">COUNTA(K32:VR32)</f>
         <v>0</v>

--- a/data/2026-2027/Présences.xlsx
+++ b/data/2026-2027/Présences.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FB6ECBC-A85F-CF4D-BA28-0DE3CE13F7B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D55BCB3-39AE-EA4D-A103-6BAC966A9604}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{2EF0EE96-8EE0-C649-8161-B8679CB6F342}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="933" uniqueCount="53">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -584,13 +584,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0866E353-69CC-CA42-AE0E-F860DC308060}">
-  <dimension ref="A1:AN32"/>
+  <dimension ref="A1:AP32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" ht="51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:42" ht="51" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -711,14 +711,20 @@
       <c r="AN1" s="6">
         <v>46261</v>
       </c>
+      <c r="AO1" s="6">
+        <v>46262</v>
+      </c>
+      <c r="AP1" s="6">
+        <v>46265</v>
+      </c>
     </row>
-    <row r="2" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="3">
         <f>COUNTA(K2:VR2)</f>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C2" s="3">
         <f>COUNTIF(K2:VR2,"P")</f>
@@ -730,7 +736,7 @@
       </c>
       <c r="E2" s="3">
         <f t="shared" ref="E2:E26" si="0">COUNTIF(K2:VS2,"A")</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F2" s="3">
         <f t="shared" ref="F2:F26" si="1">COUNTIF(K2:VT2,"B")</f>
@@ -842,18 +848,24 @@
       <c r="AN2" s="3" t="s">
         <v>18</v>
       </c>
+      <c r="AO2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AP2" s="3" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="3" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="3">
         <f t="shared" ref="B3:B21" si="2">COUNTA(K3:VR3)</f>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C3" s="3">
         <f t="shared" ref="C3:C21" si="3">COUNTIF(K3:VR3,"P")</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D3" s="5">
         <f t="shared" ref="D3:D26" si="4">COUNTIF(K3:VR3,"REP")</f>
@@ -973,18 +985,24 @@
       <c r="AN3" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AO3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AP3" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="4" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>24</v>
       </c>
       <c r="B4" s="3">
         <f t="shared" si="2"/>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C4" s="3">
         <f t="shared" si="3"/>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D4" s="5">
         <f t="shared" si="4"/>
@@ -1104,18 +1122,24 @@
       <c r="AN4" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AO4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AP4" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="3">
         <f t="shared" si="2"/>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C5" s="3">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D5" s="5">
         <f t="shared" si="4"/>
@@ -1235,18 +1259,24 @@
       <c r="AN5" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AO5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AP5" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>25</v>
       </c>
       <c r="B6" s="3">
         <f t="shared" si="2"/>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C6" s="3">
         <f t="shared" si="3"/>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D6" s="5">
         <f t="shared" si="4"/>
@@ -1366,18 +1396,24 @@
       <c r="AN6" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AO6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AP6" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>26</v>
       </c>
       <c r="B7" s="3">
         <f t="shared" si="2"/>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C7" s="3">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D7" s="5">
         <f t="shared" si="4"/>
@@ -1497,14 +1533,20 @@
       <c r="AN7" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AO7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AP7" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>27</v>
       </c>
       <c r="B8" s="3">
         <f t="shared" si="2"/>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C8" s="3">
         <f t="shared" si="3"/>
@@ -1520,7 +1562,7 @@
       </c>
       <c r="F8" s="3">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G8" s="3">
         <f t="shared" si="5"/>
@@ -1628,18 +1670,24 @@
       <c r="AN8" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="AO8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AP8" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="3">
         <f t="shared" si="2"/>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C9" s="3">
         <f t="shared" si="3"/>
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D9" s="5">
         <f t="shared" si="4"/>
@@ -1759,18 +1807,24 @@
       <c r="AN9" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AO9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AP9" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>28</v>
       </c>
       <c r="B10" s="3">
         <f t="shared" si="2"/>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C10" s="3">
         <f t="shared" si="3"/>
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D10" s="5">
         <f t="shared" si="4"/>
@@ -1890,18 +1944,24 @@
       <c r="AN10" s="3" t="s">
         <v>18</v>
       </c>
+      <c r="AO10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AP10" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="3">
         <f t="shared" si="2"/>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C11" s="3">
         <f t="shared" si="3"/>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D11" s="5">
         <f t="shared" si="4"/>
@@ -2021,18 +2081,24 @@
       <c r="AN11" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AO11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AP11" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>13</v>
       </c>
       <c r="B12" s="3">
         <f t="shared" si="2"/>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C12" s="3">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D12" s="5">
         <f t="shared" si="4"/>
@@ -2152,18 +2218,24 @@
       <c r="AN12" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AO12" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AP12" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>23</v>
       </c>
       <c r="B13" s="3">
         <f t="shared" si="2"/>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C13" s="3">
         <f t="shared" si="3"/>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D13" s="5">
         <f t="shared" si="4"/>
@@ -2283,18 +2355,24 @@
       <c r="AN13" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AO13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AP13" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>14</v>
       </c>
       <c r="B14" s="3">
         <f t="shared" si="2"/>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C14" s="3">
         <f t="shared" si="3"/>
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D14" s="5">
         <f t="shared" si="4"/>
@@ -2414,18 +2492,24 @@
       <c r="AN14" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AO14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AP14" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>29</v>
       </c>
       <c r="B15" s="3">
         <f t="shared" si="2"/>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C15" s="3">
         <f t="shared" si="3"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D15" s="5">
         <f t="shared" si="4"/>
@@ -2445,7 +2529,7 @@
       </c>
       <c r="H15" s="3">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I15" s="3">
         <f t="shared" si="7"/>
@@ -2545,18 +2629,24 @@
       <c r="AN15" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AO15" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="AP15" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>30</v>
       </c>
       <c r="B16" s="3">
         <f t="shared" si="2"/>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C16" s="3">
         <f t="shared" si="3"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D16" s="5">
         <f t="shared" si="4"/>
@@ -2576,7 +2666,7 @@
       </c>
       <c r="H16" s="3">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I16" s="3">
         <f t="shared" si="7"/>
@@ -2676,18 +2766,24 @@
       <c r="AN16" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AO16" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="AP16" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="17" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>31</v>
       </c>
       <c r="B17" s="3">
         <f t="shared" si="2"/>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C17" s="3">
         <f t="shared" si="3"/>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D17" s="5">
         <f t="shared" si="4"/>
@@ -2807,18 +2903,24 @@
       <c r="AN17" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AO17" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AP17" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="18" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>21</v>
       </c>
       <c r="B18" s="3">
         <f t="shared" si="2"/>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C18" s="3">
         <f t="shared" si="3"/>
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D18" s="5">
         <f t="shared" si="4"/>
@@ -2938,18 +3040,24 @@
       <c r="AN18" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AO18" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AP18" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="19" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>16</v>
       </c>
       <c r="B19" s="3">
         <f t="shared" si="2"/>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C19" s="3">
         <f t="shared" si="3"/>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D19" s="5">
         <f t="shared" si="4"/>
@@ -3069,18 +3177,24 @@
       <c r="AN19" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AO19" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AP19" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="20" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>37</v>
       </c>
       <c r="B20" s="3">
         <f t="shared" si="2"/>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C20" s="3">
         <f t="shared" si="3"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D20" s="5">
         <f t="shared" si="4"/>
@@ -3100,7 +3214,7 @@
       </c>
       <c r="H20" s="3">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I20" s="3">
         <f t="shared" si="7"/>
@@ -3200,18 +3314,24 @@
       <c r="AN20" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AO20" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="AP20" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="21" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>32</v>
       </c>
       <c r="B21" s="3">
         <f t="shared" si="2"/>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C21" s="3">
         <f t="shared" si="3"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D21" s="5">
         <f t="shared" si="4"/>
@@ -3231,7 +3351,7 @@
       </c>
       <c r="H21" s="3">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I21" s="3">
         <f t="shared" si="7"/>
@@ -3331,18 +3451,24 @@
       <c r="AN21" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AO21" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="AP21" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="22" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>33</v>
       </c>
       <c r="B22" s="3">
         <f t="shared" ref="B22:B26" si="9">COUNTA(K22:VR22)</f>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C22" s="3">
         <f t="shared" ref="C22:C26" si="10">COUNTIF(K22:VR22,"P")</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D22" s="5">
         <f t="shared" si="4"/>
@@ -3362,7 +3488,7 @@
       </c>
       <c r="H22" s="3">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I22" s="3">
         <f t="shared" si="7"/>
@@ -3462,18 +3588,24 @@
       <c r="AN22" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AO22" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="AP22" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="23" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>34</v>
       </c>
       <c r="B23" s="3">
         <f t="shared" si="9"/>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C23" s="3">
         <f t="shared" si="10"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D23" s="5">
         <f t="shared" si="4"/>
@@ -3493,7 +3625,7 @@
       </c>
       <c r="H23" s="3">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I23" s="3">
         <f t="shared" si="7"/>
@@ -3593,18 +3725,24 @@
       <c r="AN23" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AO23" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="AP23" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="24" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>36</v>
       </c>
       <c r="B24" s="3">
         <f t="shared" si="9"/>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C24" s="3">
         <f t="shared" si="10"/>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D24" s="5">
         <f t="shared" si="4"/>
@@ -3724,18 +3862,24 @@
       <c r="AN24" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AO24" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AP24" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="25" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>35</v>
       </c>
       <c r="B25" s="3">
         <f t="shared" si="9"/>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C25" s="3">
         <f t="shared" si="10"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D25" s="5">
         <f t="shared" si="4"/>
@@ -3743,7 +3887,7 @@
       </c>
       <c r="E25" s="3">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F25" s="3">
         <f t="shared" si="1"/>
@@ -3855,18 +3999,24 @@
       <c r="AN25" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AO25" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AP25" s="3" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="26" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>15</v>
       </c>
       <c r="B26" s="3">
         <f t="shared" si="9"/>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C26" s="3">
         <f t="shared" si="10"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D26" s="5">
         <f t="shared" si="4"/>
@@ -3886,7 +4036,7 @@
       </c>
       <c r="H26" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" s="3">
         <f t="shared" si="7"/>
@@ -3986,18 +4136,24 @@
       <c r="AN26" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AO26" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="AP26" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="27" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>38</v>
       </c>
       <c r="B27" s="3">
         <f t="shared" ref="B27:B29" si="11">COUNTA(K27:VR27)</f>
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C27" s="3">
         <f t="shared" ref="C27:C29" si="12">COUNTIF(K27:VR27,"P")</f>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D27" s="5">
         <f t="shared" ref="D27:D29" si="13">COUNTIF(K27:VR27,"REP")</f>
@@ -4111,18 +4267,24 @@
       <c r="AN27" s="3" t="s">
         <v>47</v>
       </c>
+      <c r="AO27" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AP27" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="28" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>39</v>
       </c>
       <c r="B28" s="3">
         <f t="shared" si="11"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C28" s="3">
         <f t="shared" si="12"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D28" s="5">
         <f t="shared" si="13"/>
@@ -4230,18 +4392,24 @@
       <c r="AN28" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AO28" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AP28" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="29" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>48</v>
       </c>
       <c r="B29" s="3">
         <f t="shared" si="11"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C29" s="3">
         <f t="shared" si="12"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D29" s="5">
         <f t="shared" si="13"/>
@@ -4295,18 +4463,24 @@
       <c r="AN29" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AO29" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AP29" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="30" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>49</v>
       </c>
       <c r="B30" s="3">
         <f t="shared" ref="B30" si="20">COUNTA(K30:VR30)</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C30" s="3">
         <f t="shared" ref="C30" si="21">COUNTIF(K30:VR30,"P")</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D30" s="5">
         <f t="shared" ref="D30" si="22">COUNTIF(K30:VR30,"REP")</f>
@@ -4360,18 +4534,24 @@
       <c r="AN30" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AO30" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AP30" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="31" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>52</v>
       </c>
       <c r="B31" s="3">
         <f t="shared" ref="B31" si="29">COUNTA(K31:VR31)</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C31" s="3">
         <f t="shared" ref="C31" si="30">COUNTIF(K31:VR31,"P")</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D31" s="5">
         <f t="shared" ref="D31" si="31">COUNTIF(K31:VR31,"REP")</f>
@@ -4425,8 +4605,14 @@
       <c r="AN31" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AO31" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AP31" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="32" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B32" s="3">
         <f t="shared" ref="B32" si="38">COUNTA(K32:VR32)</f>
         <v>0</v>

--- a/data/2026-2027/Présences.xlsx
+++ b/data/2026-2027/Présences.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D55BCB3-39AE-EA4D-A103-6BAC966A9604}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5D60A9E-964E-384E-9C36-68FCB87C0307}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{2EF0EE96-8EE0-C649-8161-B8679CB6F342}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="933" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="963" uniqueCount="53">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -584,13 +584,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0866E353-69CC-CA42-AE0E-F860DC308060}">
-  <dimension ref="A1:AP32"/>
+  <dimension ref="A1:AQ32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42" ht="51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:43" ht="51" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -717,14 +717,17 @@
       <c r="AP1" s="6">
         <v>46265</v>
       </c>
+      <c r="AQ1" s="6">
+        <v>46266</v>
+      </c>
     </row>
-    <row r="2" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="3">
         <f>COUNTA(K2:VR2)</f>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C2" s="3">
         <f>COUNTIF(K2:VR2,"P")</f>
@@ -736,7 +739,7 @@
       </c>
       <c r="E2" s="3">
         <f t="shared" ref="E2:E26" si="0">COUNTIF(K2:VS2,"A")</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2" s="3">
         <f t="shared" ref="F2:F26" si="1">COUNTIF(K2:VT2,"B")</f>
@@ -854,18 +857,21 @@
       <c r="AP2" s="3" t="s">
         <v>18</v>
       </c>
+      <c r="AQ2" s="3" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="3" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="3">
         <f t="shared" ref="B3:B21" si="2">COUNTA(K3:VR3)</f>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C3" s="3">
         <f t="shared" ref="C3:C21" si="3">COUNTIF(K3:VR3,"P")</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D3" s="5">
         <f t="shared" ref="D3:D26" si="4">COUNTIF(K3:VR3,"REP")</f>
@@ -991,18 +997,21 @@
       <c r="AP3" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AQ3" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="4" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>24</v>
       </c>
       <c r="B4" s="3">
         <f t="shared" si="2"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C4" s="3">
         <f t="shared" si="3"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D4" s="5">
         <f t="shared" si="4"/>
@@ -1128,18 +1137,21 @@
       <c r="AP4" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AQ4" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="3">
         <f t="shared" si="2"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C5" s="3">
         <f t="shared" si="3"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D5" s="5">
         <f t="shared" si="4"/>
@@ -1265,18 +1277,21 @@
       <c r="AP5" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AQ5" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>25</v>
       </c>
       <c r="B6" s="3">
         <f t="shared" si="2"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C6" s="3">
         <f t="shared" si="3"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D6" s="5">
         <f t="shared" si="4"/>
@@ -1402,18 +1417,21 @@
       <c r="AP6" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AQ6" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>26</v>
       </c>
       <c r="B7" s="3">
         <f t="shared" si="2"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C7" s="3">
         <f t="shared" si="3"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D7" s="5">
         <f t="shared" si="4"/>
@@ -1539,14 +1557,17 @@
       <c r="AP7" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AQ7" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>27</v>
       </c>
       <c r="B8" s="3">
         <f t="shared" si="2"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C8" s="3">
         <f t="shared" si="3"/>
@@ -1562,7 +1583,7 @@
       </c>
       <c r="F8" s="3">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G8" s="3">
         <f t="shared" si="5"/>
@@ -1676,18 +1697,21 @@
       <c r="AP8" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="AQ8" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="3">
         <f t="shared" si="2"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C9" s="3">
         <f t="shared" si="3"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D9" s="5">
         <f t="shared" si="4"/>
@@ -1813,18 +1837,21 @@
       <c r="AP9" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AQ9" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>28</v>
       </c>
       <c r="B10" s="3">
         <f t="shared" si="2"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C10" s="3">
         <f t="shared" si="3"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D10" s="5">
         <f t="shared" si="4"/>
@@ -1950,18 +1977,21 @@
       <c r="AP10" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AQ10" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="3">
         <f t="shared" si="2"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C11" s="3">
         <f t="shared" si="3"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D11" s="5">
         <f t="shared" si="4"/>
@@ -2087,18 +2117,21 @@
       <c r="AP11" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AQ11" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>13</v>
       </c>
       <c r="B12" s="3">
         <f t="shared" si="2"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C12" s="3">
         <f t="shared" si="3"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D12" s="5">
         <f t="shared" si="4"/>
@@ -2224,18 +2257,21 @@
       <c r="AP12" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>23</v>
       </c>
       <c r="B13" s="3">
         <f t="shared" si="2"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C13" s="3">
         <f t="shared" si="3"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D13" s="5">
         <f t="shared" si="4"/>
@@ -2361,18 +2397,21 @@
       <c r="AP13" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AQ13" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>14</v>
       </c>
       <c r="B14" s="3">
         <f t="shared" si="2"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C14" s="3">
         <f t="shared" si="3"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D14" s="5">
         <f t="shared" si="4"/>
@@ -2498,18 +2537,21 @@
       <c r="AP14" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AQ14" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>29</v>
       </c>
       <c r="B15" s="3">
         <f t="shared" si="2"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C15" s="3">
         <f t="shared" si="3"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D15" s="5">
         <f t="shared" si="4"/>
@@ -2635,18 +2677,21 @@
       <c r="AP15" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AQ15" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>30</v>
       </c>
       <c r="B16" s="3">
         <f t="shared" si="2"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C16" s="3">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D16" s="5">
         <f t="shared" si="4"/>
@@ -2772,18 +2817,21 @@
       <c r="AP16" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AQ16" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="17" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>31</v>
       </c>
       <c r="B17" s="3">
         <f t="shared" si="2"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C17" s="3">
         <f t="shared" si="3"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D17" s="5">
         <f t="shared" si="4"/>
@@ -2909,18 +2957,21 @@
       <c r="AP17" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AQ17" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="18" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>21</v>
       </c>
       <c r="B18" s="3">
         <f t="shared" si="2"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C18" s="3">
         <f t="shared" si="3"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D18" s="5">
         <f t="shared" si="4"/>
@@ -3046,18 +3097,21 @@
       <c r="AP18" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AQ18" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="19" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>16</v>
       </c>
       <c r="B19" s="3">
         <f t="shared" si="2"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C19" s="3">
         <f t="shared" si="3"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D19" s="5">
         <f t="shared" si="4"/>
@@ -3183,18 +3237,21 @@
       <c r="AP19" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AQ19" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="20" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>37</v>
       </c>
       <c r="B20" s="3">
         <f t="shared" si="2"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C20" s="3">
         <f t="shared" si="3"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D20" s="5">
         <f t="shared" si="4"/>
@@ -3320,18 +3377,21 @@
       <c r="AP20" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AQ20" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="21" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>32</v>
       </c>
       <c r="B21" s="3">
         <f t="shared" si="2"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C21" s="3">
         <f t="shared" si="3"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D21" s="5">
         <f t="shared" si="4"/>
@@ -3457,18 +3517,21 @@
       <c r="AP21" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AQ21" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="22" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>33</v>
       </c>
       <c r="B22" s="3">
         <f t="shared" ref="B22:B26" si="9">COUNTA(K22:VR22)</f>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C22" s="3">
         <f t="shared" ref="C22:C26" si="10">COUNTIF(K22:VR22,"P")</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D22" s="5">
         <f t="shared" si="4"/>
@@ -3594,18 +3657,21 @@
       <c r="AP22" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AQ22" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="23" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>34</v>
       </c>
       <c r="B23" s="3">
         <f t="shared" si="9"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C23" s="3">
         <f t="shared" si="10"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D23" s="5">
         <f t="shared" si="4"/>
@@ -3731,18 +3797,21 @@
       <c r="AP23" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AQ23" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="24" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>36</v>
       </c>
       <c r="B24" s="3">
         <f t="shared" si="9"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C24" s="3">
         <f t="shared" si="10"/>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D24" s="5">
         <f t="shared" si="4"/>
@@ -3868,18 +3937,21 @@
       <c r="AP24" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AQ24" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="25" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>35</v>
       </c>
       <c r="B25" s="3">
         <f t="shared" si="9"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C25" s="3">
         <f t="shared" si="10"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D25" s="5">
         <f t="shared" si="4"/>
@@ -4005,18 +4077,21 @@
       <c r="AP25" s="3" t="s">
         <v>18</v>
       </c>
+      <c r="AQ25" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="26" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>15</v>
       </c>
       <c r="B26" s="3">
         <f t="shared" si="9"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C26" s="3">
         <f t="shared" si="10"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D26" s="5">
         <f t="shared" si="4"/>
@@ -4142,18 +4217,21 @@
       <c r="AP26" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AQ26" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="27" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>38</v>
       </c>
       <c r="B27" s="3">
         <f t="shared" ref="B27:B29" si="11">COUNTA(K27:VR27)</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C27" s="3">
         <f t="shared" ref="C27:C29" si="12">COUNTIF(K27:VR27,"P")</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D27" s="5">
         <f t="shared" ref="D27:D29" si="13">COUNTIF(K27:VR27,"REP")</f>
@@ -4273,18 +4351,21 @@
       <c r="AP27" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AQ27" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="28" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>39</v>
       </c>
       <c r="B28" s="3">
         <f t="shared" si="11"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C28" s="3">
         <f t="shared" si="12"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D28" s="5">
         <f t="shared" si="13"/>
@@ -4398,18 +4479,21 @@
       <c r="AP28" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AQ28" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="29" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>48</v>
       </c>
       <c r="B29" s="3">
         <f t="shared" si="11"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C29" s="3">
         <f t="shared" si="12"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D29" s="5">
         <f t="shared" si="13"/>
@@ -4469,14 +4553,17 @@
       <c r="AP29" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="30" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>49</v>
       </c>
       <c r="B30" s="3">
         <f t="shared" ref="B30" si="20">COUNTA(K30:VR30)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C30" s="3">
         <f t="shared" ref="C30" si="21">COUNTIF(K30:VR30,"P")</f>
@@ -4492,7 +4579,7 @@
       </c>
       <c r="F30" s="3">
         <f t="shared" ref="F30" si="24">COUNTIF(K30:VT30,"B")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G30" s="3">
         <f t="shared" ref="G30" si="25">COUNTIF(K30:VU30,"M")</f>
@@ -4540,18 +4627,21 @@
       <c r="AP30" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AQ30" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="31" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>52</v>
       </c>
       <c r="B31" s="3">
         <f t="shared" ref="B31" si="29">COUNTA(K31:VR31)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C31" s="3">
         <f t="shared" ref="C31" si="30">COUNTIF(K31:VR31,"P")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D31" s="5">
         <f t="shared" ref="D31" si="31">COUNTIF(K31:VR31,"REP")</f>
@@ -4611,8 +4701,11 @@
       <c r="AP31" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AQ31" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="32" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B32" s="3">
         <f t="shared" ref="B32" si="38">COUNTA(K32:VR32)</f>
         <v>0</v>

--- a/data/2026-2027/Présences.xlsx
+++ b/data/2026-2027/Présences.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5D60A9E-964E-384E-9C36-68FCB87C0307}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E3C42D2-1611-834C-B3FA-BEA8730FEC4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{2EF0EE96-8EE0-C649-8161-B8679CB6F342}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="963" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="993" uniqueCount="53">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -584,13 +584,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0866E353-69CC-CA42-AE0E-F860DC308060}">
-  <dimension ref="A1:AQ32"/>
+  <dimension ref="A1:AR32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" ht="51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:44" ht="51" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -720,14 +720,17 @@
       <c r="AQ1" s="6">
         <v>46266</v>
       </c>
+      <c r="AR1" s="6">
+        <v>46267</v>
+      </c>
     </row>
-    <row r="2" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="3">
         <f>COUNTA(K2:VR2)</f>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C2" s="3">
         <f>COUNTIF(K2:VR2,"P")</f>
@@ -739,7 +742,7 @@
       </c>
       <c r="E2" s="3">
         <f t="shared" ref="E2:E26" si="0">COUNTIF(K2:VS2,"A")</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F2" s="3">
         <f t="shared" ref="F2:F26" si="1">COUNTIF(K2:VT2,"B")</f>
@@ -860,18 +863,21 @@
       <c r="AQ2" s="3" t="s">
         <v>18</v>
       </c>
+      <c r="AR2" s="3" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="3" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="3">
         <f t="shared" ref="B3:B21" si="2">COUNTA(K3:VR3)</f>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C3" s="3">
         <f t="shared" ref="C3:C21" si="3">COUNTIF(K3:VR3,"P")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D3" s="5">
         <f t="shared" ref="D3:D26" si="4">COUNTIF(K3:VR3,"REP")</f>
@@ -1000,18 +1006,21 @@
       <c r="AQ3" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AR3" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="4" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>24</v>
       </c>
       <c r="B4" s="3">
         <f t="shared" si="2"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C4" s="3">
         <f t="shared" si="3"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D4" s="5">
         <f t="shared" si="4"/>
@@ -1140,18 +1149,21 @@
       <c r="AQ4" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AR4" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="3">
         <f t="shared" si="2"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C5" s="3">
         <f t="shared" si="3"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D5" s="5">
         <f t="shared" si="4"/>
@@ -1280,18 +1292,21 @@
       <c r="AQ5" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AR5" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>25</v>
       </c>
       <c r="B6" s="3">
         <f t="shared" si="2"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C6" s="3">
         <f t="shared" si="3"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D6" s="5">
         <f t="shared" si="4"/>
@@ -1420,14 +1435,17 @@
       <c r="AQ6" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AR6" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>26</v>
       </c>
       <c r="B7" s="3">
         <f t="shared" si="2"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C7" s="3">
         <f t="shared" si="3"/>
@@ -1451,7 +1469,7 @@
       </c>
       <c r="H7" s="3">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I7" s="3">
         <f t="shared" si="7"/>
@@ -1560,14 +1578,17 @@
       <c r="AQ7" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AR7" s="3" t="s">
+        <v>51</v>
+      </c>
     </row>
-    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>27</v>
       </c>
       <c r="B8" s="3">
         <f t="shared" si="2"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C8" s="3">
         <f t="shared" si="3"/>
@@ -1583,7 +1604,7 @@
       </c>
       <c r="F8" s="3">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G8" s="3">
         <f t="shared" si="5"/>
@@ -1700,18 +1721,21 @@
       <c r="AQ8" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="AR8" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="3">
         <f t="shared" si="2"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C9" s="3">
         <f t="shared" si="3"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D9" s="5">
         <f t="shared" si="4"/>
@@ -1840,14 +1864,17 @@
       <c r="AQ9" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AR9" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>28</v>
       </c>
       <c r="B10" s="3">
         <f t="shared" si="2"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" s="3">
         <f t="shared" si="3"/>
@@ -1863,7 +1890,7 @@
       </c>
       <c r="F10" s="3">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G10" s="3">
         <f t="shared" si="5"/>
@@ -1980,18 +2007,21 @@
       <c r="AQ10" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AR10" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="3">
         <f t="shared" si="2"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C11" s="3">
         <f t="shared" si="3"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D11" s="5">
         <f t="shared" si="4"/>
@@ -2120,18 +2150,21 @@
       <c r="AQ11" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AR11" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>13</v>
       </c>
       <c r="B12" s="3">
         <f t="shared" si="2"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" s="3">
         <f t="shared" si="3"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D12" s="5">
         <f t="shared" si="4"/>
@@ -2260,18 +2293,21 @@
       <c r="AQ12" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AR12" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>23</v>
       </c>
       <c r="B13" s="3">
         <f t="shared" si="2"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C13" s="3">
         <f t="shared" si="3"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D13" s="5">
         <f t="shared" si="4"/>
@@ -2400,18 +2436,21 @@
       <c r="AQ13" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AR13" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>14</v>
       </c>
       <c r="B14" s="3">
         <f t="shared" si="2"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C14" s="3">
         <f t="shared" si="3"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D14" s="5">
         <f t="shared" si="4"/>
@@ -2540,14 +2579,17 @@
       <c r="AQ14" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AR14" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>29</v>
       </c>
       <c r="B15" s="3">
         <f t="shared" si="2"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C15" s="3">
         <f t="shared" si="3"/>
@@ -2571,7 +2613,7 @@
       </c>
       <c r="H15" s="3">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I15" s="3">
         <f t="shared" si="7"/>
@@ -2680,14 +2722,17 @@
       <c r="AQ15" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AR15" s="3" t="s">
+        <v>51</v>
+      </c>
     </row>
-    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>30</v>
       </c>
       <c r="B16" s="3">
         <f t="shared" si="2"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C16" s="3">
         <f t="shared" si="3"/>
@@ -2711,7 +2756,7 @@
       </c>
       <c r="H16" s="3">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I16" s="3">
         <f t="shared" si="7"/>
@@ -2820,18 +2865,21 @@
       <c r="AQ16" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AR16" s="3" t="s">
+        <v>51</v>
+      </c>
     </row>
-    <row r="17" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>31</v>
       </c>
       <c r="B17" s="3">
         <f t="shared" si="2"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C17" s="3">
         <f t="shared" si="3"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D17" s="5">
         <f t="shared" si="4"/>
@@ -2960,18 +3008,21 @@
       <c r="AQ17" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AR17" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="18" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>21</v>
       </c>
       <c r="B18" s="3">
         <f t="shared" si="2"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C18" s="3">
         <f t="shared" si="3"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D18" s="5">
         <f t="shared" si="4"/>
@@ -3100,18 +3151,21 @@
       <c r="AQ18" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AR18" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="19" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>16</v>
       </c>
       <c r="B19" s="3">
         <f t="shared" si="2"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C19" s="3">
         <f t="shared" si="3"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D19" s="5">
         <f t="shared" si="4"/>
@@ -3240,18 +3294,21 @@
       <c r="AQ19" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AR19" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="20" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>37</v>
       </c>
       <c r="B20" s="3">
         <f t="shared" si="2"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C20" s="3">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D20" s="5">
         <f t="shared" si="4"/>
@@ -3380,14 +3437,17 @@
       <c r="AQ20" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AR20" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="21" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>32</v>
       </c>
       <c r="B21" s="3">
         <f t="shared" si="2"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C21" s="3">
         <f t="shared" si="3"/>
@@ -3411,7 +3471,7 @@
       </c>
       <c r="H21" s="3">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I21" s="3">
         <f t="shared" si="7"/>
@@ -3520,14 +3580,17 @@
       <c r="AQ21" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AR21" s="3" t="s">
+        <v>51</v>
+      </c>
     </row>
-    <row r="22" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>33</v>
       </c>
       <c r="B22" s="3">
         <f t="shared" ref="B22:B26" si="9">COUNTA(K22:VR22)</f>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C22" s="3">
         <f t="shared" ref="C22:C26" si="10">COUNTIF(K22:VR22,"P")</f>
@@ -3551,7 +3614,7 @@
       </c>
       <c r="H22" s="3">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I22" s="3">
         <f t="shared" si="7"/>
@@ -3660,18 +3723,21 @@
       <c r="AQ22" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AR22" s="3" t="s">
+        <v>51</v>
+      </c>
     </row>
-    <row r="23" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>34</v>
       </c>
       <c r="B23" s="3">
         <f t="shared" si="9"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C23" s="3">
         <f t="shared" si="10"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D23" s="5">
         <f t="shared" si="4"/>
@@ -3800,18 +3866,21 @@
       <c r="AQ23" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AR23" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="24" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>36</v>
       </c>
       <c r="B24" s="3">
         <f t="shared" si="9"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C24" s="3">
         <f t="shared" si="10"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D24" s="5">
         <f t="shared" si="4"/>
@@ -3940,18 +4009,21 @@
       <c r="AQ24" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AR24" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="25" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>35</v>
       </c>
       <c r="B25" s="3">
         <f t="shared" si="9"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C25" s="3">
         <f t="shared" si="10"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D25" s="5">
         <f t="shared" si="4"/>
@@ -4080,18 +4152,21 @@
       <c r="AQ25" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AR25" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="26" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>15</v>
       </c>
       <c r="B26" s="3">
         <f t="shared" si="9"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C26" s="3">
         <f t="shared" si="10"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D26" s="5">
         <f t="shared" si="4"/>
@@ -4220,18 +4295,21 @@
       <c r="AQ26" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AR26" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="27" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>38</v>
       </c>
       <c r="B27" s="3">
         <f t="shared" ref="B27:B29" si="11">COUNTA(K27:VR27)</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C27" s="3">
         <f t="shared" ref="C27:C29" si="12">COUNTIF(K27:VR27,"P")</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D27" s="5">
         <f t="shared" ref="D27:D29" si="13">COUNTIF(K27:VR27,"REP")</f>
@@ -4354,18 +4432,21 @@
       <c r="AQ27" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AR27" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="28" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>39</v>
       </c>
       <c r="B28" s="3">
         <f t="shared" si="11"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C28" s="3">
         <f t="shared" si="12"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D28" s="5">
         <f t="shared" si="13"/>
@@ -4482,18 +4563,21 @@
       <c r="AQ28" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AR28" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="29" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>48</v>
       </c>
       <c r="B29" s="3">
         <f t="shared" si="11"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C29" s="3">
         <f t="shared" si="12"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D29" s="5">
         <f t="shared" si="13"/>
@@ -4556,14 +4640,17 @@
       <c r="AQ29" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AR29" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="30" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>49</v>
       </c>
       <c r="B30" s="3">
         <f t="shared" ref="B30" si="20">COUNTA(K30:VR30)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C30" s="3">
         <f t="shared" ref="C30" si="21">COUNTIF(K30:VR30,"P")</f>
@@ -4591,7 +4678,7 @@
       </c>
       <c r="I30" s="3">
         <f t="shared" ref="I30" si="27">COUNTIF(K30:VW30,"RH")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J30" s="3">
         <f t="shared" ref="J30" si="28">COUNTIF(K30:VW30,"S")</f>
@@ -4630,18 +4717,21 @@
       <c r="AQ30" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="AR30" s="3" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="31" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>52</v>
       </c>
       <c r="B31" s="3">
         <f t="shared" ref="B31" si="29">COUNTA(K31:VR31)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C31" s="3">
         <f t="shared" ref="C31" si="30">COUNTIF(K31:VR31,"P")</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D31" s="5">
         <f t="shared" ref="D31" si="31">COUNTIF(K31:VR31,"REP")</f>
@@ -4704,8 +4794,11 @@
       <c r="AQ31" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AR31" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="32" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:44" x14ac:dyDescent="0.2">
       <c r="B32" s="3">
         <f t="shared" ref="B32" si="38">COUNTA(K32:VR32)</f>
         <v>0</v>

--- a/data/2026-2027/Présences.xlsx
+++ b/data/2026-2027/Présences.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E3C42D2-1611-834C-B3FA-BEA8730FEC4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5E42AC3-78BE-6C4F-A536-5EE7CED8A179}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{2EF0EE96-8EE0-C649-8161-B8679CB6F342}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="993" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1023" uniqueCount="53">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -584,13 +584,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0866E353-69CC-CA42-AE0E-F860DC308060}">
-  <dimension ref="A1:AR32"/>
+  <dimension ref="A1:AS32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" ht="51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:45" ht="51" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -723,14 +723,17 @@
       <c r="AR1" s="6">
         <v>46267</v>
       </c>
+      <c r="AS1" s="6">
+        <v>46268</v>
+      </c>
     </row>
-    <row r="2" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="3">
         <f>COUNTA(K2:VR2)</f>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C2" s="3">
         <f>COUNTIF(K2:VR2,"P")</f>
@@ -742,7 +745,7 @@
       </c>
       <c r="E2" s="3">
         <f t="shared" ref="E2:E26" si="0">COUNTIF(K2:VS2,"A")</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F2" s="3">
         <f t="shared" ref="F2:F26" si="1">COUNTIF(K2:VT2,"B")</f>
@@ -866,18 +869,21 @@
       <c r="AR2" s="3" t="s">
         <v>18</v>
       </c>
+      <c r="AS2" s="3" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="3" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="3">
         <f t="shared" ref="B3:B21" si="2">COUNTA(K3:VR3)</f>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C3" s="3">
         <f t="shared" ref="C3:C21" si="3">COUNTIF(K3:VR3,"P")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D3" s="5">
         <f t="shared" ref="D3:D26" si="4">COUNTIF(K3:VR3,"REP")</f>
@@ -1009,18 +1015,21 @@
       <c r="AR3" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AS3" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="4" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>24</v>
       </c>
       <c r="B4" s="3">
         <f t="shared" si="2"/>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C4" s="3">
         <f t="shared" si="3"/>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D4" s="5">
         <f t="shared" si="4"/>
@@ -1152,18 +1161,21 @@
       <c r="AR4" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AS4" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="5" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="3">
         <f t="shared" si="2"/>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C5" s="3">
         <f t="shared" si="3"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D5" s="5">
         <f t="shared" si="4"/>
@@ -1295,18 +1307,21 @@
       <c r="AR5" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AS5" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="6" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>25</v>
       </c>
       <c r="B6" s="3">
         <f t="shared" si="2"/>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C6" s="3">
         <f t="shared" si="3"/>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D6" s="5">
         <f t="shared" si="4"/>
@@ -1438,14 +1453,17 @@
       <c r="AR6" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AS6" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="7" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>26</v>
       </c>
       <c r="B7" s="3">
         <f t="shared" si="2"/>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C7" s="3">
         <f t="shared" si="3"/>
@@ -1469,7 +1487,7 @@
       </c>
       <c r="H7" s="3">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I7" s="3">
         <f t="shared" si="7"/>
@@ -1581,14 +1599,17 @@
       <c r="AR7" s="3" t="s">
         <v>51</v>
       </c>
+      <c r="AS7" s="3" t="s">
+        <v>51</v>
+      </c>
     </row>
-    <row r="8" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>27</v>
       </c>
       <c r="B8" s="3">
         <f t="shared" si="2"/>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C8" s="3">
         <f t="shared" si="3"/>
@@ -1604,7 +1625,7 @@
       </c>
       <c r="F8" s="3">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G8" s="3">
         <f t="shared" si="5"/>
@@ -1724,14 +1745,17 @@
       <c r="AR8" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="AS8" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="9" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="3">
         <f t="shared" si="2"/>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C9" s="3">
         <f t="shared" si="3"/>
@@ -1739,7 +1763,7 @@
       </c>
       <c r="D9" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" s="3">
         <f t="shared" si="0"/>
@@ -1867,14 +1891,17 @@
       <c r="AR9" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AS9" s="3" t="s">
+        <v>47</v>
+      </c>
     </row>
-    <row r="10" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>28</v>
       </c>
       <c r="B10" s="3">
         <f t="shared" si="2"/>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C10" s="3">
         <f t="shared" si="3"/>
@@ -1890,7 +1917,7 @@
       </c>
       <c r="F10" s="3">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G10" s="3">
         <f t="shared" si="5"/>
@@ -2010,18 +2037,21 @@
       <c r="AR10" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="AS10" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="11" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="3">
         <f t="shared" si="2"/>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C11" s="3">
         <f t="shared" si="3"/>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D11" s="5">
         <f t="shared" si="4"/>
@@ -2153,18 +2183,21 @@
       <c r="AR11" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AS11" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="12" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>13</v>
       </c>
       <c r="B12" s="3">
         <f t="shared" si="2"/>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C12" s="3">
         <f t="shared" si="3"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D12" s="5">
         <f t="shared" si="4"/>
@@ -2296,18 +2329,21 @@
       <c r="AR12" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AS12" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="13" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>23</v>
       </c>
       <c r="B13" s="3">
         <f t="shared" si="2"/>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C13" s="3">
         <f t="shared" si="3"/>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D13" s="5">
         <f t="shared" si="4"/>
@@ -2439,18 +2475,21 @@
       <c r="AR13" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AS13" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="14" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>14</v>
       </c>
       <c r="B14" s="3">
         <f t="shared" si="2"/>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C14" s="3">
         <f t="shared" si="3"/>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D14" s="5">
         <f t="shared" si="4"/>
@@ -2582,14 +2621,17 @@
       <c r="AR14" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AS14" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="15" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>29</v>
       </c>
       <c r="B15" s="3">
         <f t="shared" si="2"/>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C15" s="3">
         <f t="shared" si="3"/>
@@ -2613,7 +2655,7 @@
       </c>
       <c r="H15" s="3">
         <f t="shared" si="6"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I15" s="3">
         <f t="shared" si="7"/>
@@ -2725,14 +2767,17 @@
       <c r="AR15" s="3" t="s">
         <v>51</v>
       </c>
+      <c r="AS15" s="3" t="s">
+        <v>51</v>
+      </c>
     </row>
-    <row r="16" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>30</v>
       </c>
       <c r="B16" s="3">
         <f t="shared" si="2"/>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C16" s="3">
         <f t="shared" si="3"/>
@@ -2756,7 +2801,7 @@
       </c>
       <c r="H16" s="3">
         <f t="shared" si="6"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I16" s="3">
         <f t="shared" si="7"/>
@@ -2868,18 +2913,21 @@
       <c r="AR16" s="3" t="s">
         <v>51</v>
       </c>
+      <c r="AS16" s="3" t="s">
+        <v>51</v>
+      </c>
     </row>
-    <row r="17" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>31</v>
       </c>
       <c r="B17" s="3">
         <f t="shared" si="2"/>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C17" s="3">
         <f t="shared" si="3"/>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D17" s="5">
         <f t="shared" si="4"/>
@@ -3011,18 +3059,21 @@
       <c r="AR17" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AS17" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="18" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>21</v>
       </c>
       <c r="B18" s="3">
         <f t="shared" si="2"/>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C18" s="3">
         <f t="shared" si="3"/>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D18" s="5">
         <f t="shared" si="4"/>
@@ -3154,14 +3205,17 @@
       <c r="AR18" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AS18" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="19" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>16</v>
       </c>
       <c r="B19" s="3">
         <f t="shared" si="2"/>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C19" s="3">
         <f t="shared" si="3"/>
@@ -3177,7 +3231,7 @@
       </c>
       <c r="F19" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" s="3">
         <f t="shared" si="5"/>
@@ -3297,18 +3351,21 @@
       <c r="AR19" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AS19" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="20" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>37</v>
       </c>
       <c r="B20" s="3">
         <f t="shared" si="2"/>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C20" s="3">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D20" s="5">
         <f t="shared" si="4"/>
@@ -3440,14 +3497,17 @@
       <c r="AR20" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AS20" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="21" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>32</v>
       </c>
       <c r="B21" s="3">
         <f t="shared" si="2"/>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C21" s="3">
         <f t="shared" si="3"/>
@@ -3471,7 +3531,7 @@
       </c>
       <c r="H21" s="3">
         <f t="shared" si="6"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I21" s="3">
         <f t="shared" si="7"/>
@@ -3583,14 +3643,17 @@
       <c r="AR21" s="3" t="s">
         <v>51</v>
       </c>
+      <c r="AS21" s="3" t="s">
+        <v>51</v>
+      </c>
     </row>
-    <row r="22" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>33</v>
       </c>
       <c r="B22" s="3">
         <f t="shared" ref="B22:B26" si="9">COUNTA(K22:VR22)</f>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C22" s="3">
         <f t="shared" ref="C22:C26" si="10">COUNTIF(K22:VR22,"P")</f>
@@ -3614,7 +3677,7 @@
       </c>
       <c r="H22" s="3">
         <f t="shared" si="6"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I22" s="3">
         <f t="shared" si="7"/>
@@ -3726,18 +3789,21 @@
       <c r="AR22" s="3" t="s">
         <v>51</v>
       </c>
+      <c r="AS22" s="3" t="s">
+        <v>51</v>
+      </c>
     </row>
-    <row r="23" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>34</v>
       </c>
       <c r="B23" s="3">
         <f t="shared" si="9"/>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C23" s="3">
         <f t="shared" si="10"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D23" s="5">
         <f t="shared" si="4"/>
@@ -3869,18 +3935,21 @@
       <c r="AR23" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AS23" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="24" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>36</v>
       </c>
       <c r="B24" s="3">
         <f t="shared" si="9"/>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C24" s="3">
         <f t="shared" si="10"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D24" s="5">
         <f t="shared" si="4"/>
@@ -4012,18 +4081,21 @@
       <c r="AR24" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AS24" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="25" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>35</v>
       </c>
       <c r="B25" s="3">
         <f t="shared" si="9"/>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C25" s="3">
         <f t="shared" si="10"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D25" s="5">
         <f t="shared" si="4"/>
@@ -4155,18 +4227,21 @@
       <c r="AR25" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AS25" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="26" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>15</v>
       </c>
       <c r="B26" s="3">
         <f t="shared" si="9"/>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C26" s="3">
         <f t="shared" si="10"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D26" s="5">
         <f t="shared" si="4"/>
@@ -4298,18 +4373,21 @@
       <c r="AR26" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AS26" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="27" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>38</v>
       </c>
       <c r="B27" s="3">
         <f t="shared" ref="B27:B29" si="11">COUNTA(K27:VR27)</f>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C27" s="3">
         <f t="shared" ref="C27:C29" si="12">COUNTIF(K27:VR27,"P")</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D27" s="5">
         <f t="shared" ref="D27:D29" si="13">COUNTIF(K27:VR27,"REP")</f>
@@ -4435,18 +4513,21 @@
       <c r="AR27" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AS27" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="28" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>39</v>
       </c>
       <c r="B28" s="3">
         <f t="shared" si="11"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C28" s="3">
         <f t="shared" si="12"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D28" s="5">
         <f t="shared" si="13"/>
@@ -4566,18 +4647,21 @@
       <c r="AR28" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AS28" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="29" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>48</v>
       </c>
       <c r="B29" s="3">
         <f t="shared" si="11"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C29" s="3">
         <f t="shared" si="12"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D29" s="5">
         <f t="shared" si="13"/>
@@ -4643,14 +4727,17 @@
       <c r="AR29" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AS29" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="30" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>49</v>
       </c>
       <c r="B30" s="3">
         <f t="shared" ref="B30" si="20">COUNTA(K30:VR30)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C30" s="3">
         <f t="shared" ref="C30" si="21">COUNTIF(K30:VR30,"P")</f>
@@ -4678,7 +4765,7 @@
       </c>
       <c r="I30" s="3">
         <f t="shared" ref="I30" si="27">COUNTIF(K30:VW30,"RH")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J30" s="3">
         <f t="shared" ref="J30" si="28">COUNTIF(K30:VW30,"S")</f>
@@ -4720,18 +4807,21 @@
       <c r="AR30" s="3" t="s">
         <v>20</v>
       </c>
+      <c r="AS30" s="3" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="31" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>52</v>
       </c>
       <c r="B31" s="3">
         <f t="shared" ref="B31" si="29">COUNTA(K31:VR31)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C31" s="3">
         <f t="shared" ref="C31" si="30">COUNTIF(K31:VR31,"P")</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D31" s="5">
         <f t="shared" ref="D31" si="31">COUNTIF(K31:VR31,"REP")</f>
@@ -4797,8 +4887,11 @@
       <c r="AR31" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AS31" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="32" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:45" x14ac:dyDescent="0.2">
       <c r="B32" s="3">
         <f t="shared" ref="B32" si="38">COUNTA(K32:VR32)</f>
         <v>0</v>
